--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -1,25 +1,30 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Overview" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Cash Flow Statement" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="CET1 Capital" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="CET1 Ratio" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="Tier 1 Capital" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="Tier 1 Ratio" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="Total Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="Total Capital Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="Total RWAs" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="Leverage Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="LCR" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="NSFR" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="MREL Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Overview" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Balance Sheet" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profit &amp; Loss" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -192,18 +197,18 @@
 </file>
 
 <file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
             <a:r>
-              <a:t>Barclays Bank PLC — Cash Flow Summary by Year</a:t>
+              <a:t>Barclays Bank PLC — Balance Sheet Summary by Year</a:t>
             </a:r>
           </a:p>
         </rich>
@@ -235,7 +240,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -259,7 +264,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -283,7 +288,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -307,7 +312,7 @@
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
@@ -350,8 +355,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -390,13 +395,583 @@
 </file>
 
 <file path=xl/charts/chart2.xml><?xml version="1.0" encoding="utf-8"?>
-<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
   <chart>
     <title>
       <tx>
         <rich>
-          <a:bodyPr/>
-          <a:p>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Barclays Bank PLC — Profit &amp; Loss Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q13</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$13:$V$13</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q14</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$14:$V$14</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Q15</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$R$12:$V$12</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$R$15:$V$15</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart3.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Barclays Bank PLC — Statement of Changes in Equity Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y19</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$19:$AD$19</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y20</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$20:$AD$20</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y21</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$21:$AD$21</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!Y22</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$Z$18:$AD$18</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$Z$22:$AD$22</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart4.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Barclays Bank PLC — Cash Flow Summary by Year</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <layout>
+        <manualLayout>
+          <layoutTarget val="inner"/>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.1"/>
+          <y val="0.14"/>
+          <w val="0.85"/>
+          <h val="0.55"/>
+        </manualLayout>
+      </layout>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG26</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$26:$AL$26</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="1"/>
+          <order val="1"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG27</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$27:$AL$27</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="2"/>
+          <order val="2"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG28</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$28:$AL$28</f>
+            </numRef>
+          </val>
+        </ser>
+        <ser>
+          <idx val="3"/>
+          <order val="3"/>
+          <tx>
+            <strRef>
+              <f>'Overview'!AG29</f>
+            </strRef>
+          </tx>
+          <spPr>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <cat>
+            <numRef>
+              <f>'Overview'!$AH$25:$AL$25</f>
+            </numRef>
+          </cat>
+          <val>
+            <numRef>
+              <f>'Overview'!$AH$29:$AL$29</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="b"/>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <delete val="0"/>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <title>
+          <tx>
+            <rich>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+                <a:pPr>
+                  <a:defRPr/>
+                </a:pPr>
+                <a:r>
+                  <a:t>£m</a:t>
+                </a:r>
+              </a:p>
+            </rich>
+          </tx>
+        </title>
+        <majorTickMark val="out"/>
+        <minorTickMark val="none"/>
+        <tickLblPos val="nextTo"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="b"/>
+      <layout>
+        <manualLayout>
+          <xMode val="edge"/>
+          <yMode val="edge"/>
+          <wMode val="factor"/>
+          <hMode val="factor"/>
+          <x val="0.02"/>
+          <y val="0.84"/>
+          <w val="0.96"/>
+          <h val="0.16"/>
+        </manualLayout>
+      </layout>
+    </legend>
+    <plotVisOnly val="0"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/charts/chart5.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+          <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
             <a:pPr>
               <a:defRPr/>
             </a:pPr>
@@ -428,30 +1003,30 @@
           <order val="0"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q6</f>
+              <f>'Overview'!AO6</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$6:$V$6</f>
+              <f>'Overview'!$AP$6:$AT$6</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -461,30 +1036,30 @@
           <order val="1"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q7</f>
+              <f>'Overview'!AO7</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$7:$V$7</f>
+              <f>'Overview'!$AP$7:$AT$7</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -494,30 +1069,30 @@
           <order val="2"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q8</f>
+              <f>'Overview'!AO8</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$8:$V$8</f>
+              <f>'Overview'!$AP$8:$AT$8</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -527,30 +1102,30 @@
           <order val="3"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q9</f>
+              <f>'Overview'!AO9</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$9:$V$9</f>
+              <f>'Overview'!$AP$9:$AT$9</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -560,30 +1135,30 @@
           <order val="4"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q10</f>
+              <f>'Overview'!AO10</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$10:$V$10</f>
+              <f>'Overview'!$AP$10:$AT$10</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -593,30 +1168,30 @@
           <order val="5"/>
           <tx>
             <strRef>
-              <f>'Overview'!Q11</f>
+              <f>'Overview'!AO11</f>
             </strRef>
           </tx>
           <spPr>
-            <a:ln>
+            <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
               <a:prstDash val="solid"/>
             </a:ln>
           </spPr>
           <marker>
             <symbol val="none"/>
             <spPr>
-              <a:ln>
+              <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:prstDash val="solid"/>
               </a:ln>
             </spPr>
           </marker>
           <cat>
             <numRef>
-              <f>'Overview'!$R$5:$V$5</f>
+              <f>'Overview'!$AP$5:$AT$5</f>
             </numRef>
           </cat>
           <val>
             <numRef>
-              <f>'Overview'!$R$11:$V$11</f>
+              <f>'Overview'!$AP$11:$AT$11</f>
             </numRef>
           </val>
           <smooth val="0"/>
@@ -648,8 +1223,8 @@
         <title>
           <tx>
             <rich>
-              <a:bodyPr/>
-              <a:p>
+              <a:bodyPr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main"/>
+              <a:p xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
                 <a:pPr>
                   <a:defRPr/>
                 </a:pPr>
@@ -688,12 +1263,12 @@
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
-<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
+      <row>42</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="8640000" cy="4680000"/>
@@ -703,9 +1278,9 @@
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId1"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -715,19 +1290,85 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>44</row>
+      <row>64</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="8640000" cy="5760000"/>
+    <ext cx="8640000" cy="4680000"/>
     <graphicFrame>
       <nvGraphicFramePr>
         <cNvPr id="2" name="Chart 2"/>
         <cNvGraphicFramePr/>
       </nvGraphicFramePr>
       <xfrm/>
-      <a:graphic>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
-          <c:chart r:id="rId2"/>
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>86</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="3" name="Chart 3"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>108</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="4680000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="4" name="Chart 4"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId4"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>130</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="8640000" cy="5760000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="5" name="Chart 5"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId5"/>
         </a:graphicData>
       </a:graphic>
     </graphicFrame>
@@ -1025,7 +1666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:V20"/>
+  <dimension ref="A1:AT40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1048,6 +1689,30 @@
     <col hidden="1" width="13" customWidth="1" min="20" max="20"/>
     <col hidden="1" width="13" customWidth="1" min="21" max="21"/>
     <col hidden="1" width="13" customWidth="1" min="22" max="22"/>
+    <col hidden="1" width="13" customWidth="1" min="23" max="23"/>
+    <col hidden="1" width="13" customWidth="1" min="24" max="24"/>
+    <col hidden="1" width="13" customWidth="1" min="25" max="25"/>
+    <col hidden="1" width="13" customWidth="1" min="26" max="26"/>
+    <col hidden="1" width="13" customWidth="1" min="27" max="27"/>
+    <col hidden="1" width="13" customWidth="1" min="28" max="28"/>
+    <col hidden="1" width="13" customWidth="1" min="29" max="29"/>
+    <col hidden="1" width="13" customWidth="1" min="30" max="30"/>
+    <col hidden="1" width="13" customWidth="1" min="31" max="31"/>
+    <col hidden="1" width="13" customWidth="1" min="32" max="32"/>
+    <col hidden="1" width="13" customWidth="1" min="33" max="33"/>
+    <col hidden="1" width="13" customWidth="1" min="34" max="34"/>
+    <col hidden="1" width="13" customWidth="1" min="35" max="35"/>
+    <col hidden="1" width="13" customWidth="1" min="36" max="36"/>
+    <col hidden="1" width="13" customWidth="1" min="37" max="37"/>
+    <col hidden="1" width="13" customWidth="1" min="38" max="38"/>
+    <col hidden="1" width="13" customWidth="1" min="39" max="39"/>
+    <col hidden="1" width="13" customWidth="1" min="40" max="40"/>
+    <col hidden="1" width="13" customWidth="1" min="41" max="41"/>
+    <col hidden="1" width="13" customWidth="1" min="42" max="42"/>
+    <col hidden="1" width="13" customWidth="1" min="43" max="43"/>
+    <col hidden="1" width="13" customWidth="1" min="44" max="44"/>
+    <col hidden="1" width="13" customWidth="1" min="45" max="45"/>
+    <col hidden="1" width="13" customWidth="1" min="46" max="46"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1060,14 +1725,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Summary of cash flow and Pillar 3 disclosures across all years covered in this workbook</t>
+          <t>Headline balance sheet, profit &amp; loss, cash flow and Pillar 3 figures across all years covered in this workbook - how the bank is using its money and the risk it is taking with it</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
-          <t>Cash Flow Summary (£m)</t>
+          <t>Balance Sheet Summary (£m)</t>
         </is>
       </c>
     </row>
@@ -1127,27 +1792,27 @@
           <t>FY2025</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="AP5" t="inlineStr">
         <is>
           <t>FY2021</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
+      <c r="AQ5" t="inlineStr">
         <is>
           <t>FY2022</t>
         </is>
       </c>
-      <c r="T5" t="inlineStr">
+      <c r="AR5" t="inlineStr">
         <is>
           <t>FY2023</t>
         </is>
       </c>
-      <c r="U5" t="inlineStr">
+      <c r="AS5" t="inlineStr">
         <is>
           <t>FY2024</t>
         </is>
       </c>
-      <c r="V5" t="inlineStr">
+      <c r="AT5" t="inlineStr">
         <is>
           <t>FY2025</t>
         </is>
@@ -1156,294 +1821,274 @@
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="B6" s="5" t="n">
-        <v>28103</v>
+        <v>1245473</v>
       </c>
       <c r="C6" s="5" t="n">
-        <v>1991</v>
+        <v>1218524</v>
       </c>
       <c r="D6" s="5" t="n">
-        <v>16367</v>
+        <v>1185166</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>24984</v>
+        <v>1203537</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>17497</v>
+        <v>1061778</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>Net cash from operating activities</t>
+          <t>Total assets</t>
         </is>
       </c>
       <c r="J6" t="n">
-        <v>17497</v>
+        <v>1061778</v>
       </c>
       <c r="K6" t="n">
-        <v>24984</v>
+        <v>1203537</v>
       </c>
       <c r="L6" t="n">
-        <v>16367</v>
+        <v>1185166</v>
       </c>
       <c r="M6" t="n">
-        <v>1991</v>
+        <v>1218524</v>
       </c>
       <c r="N6" t="n">
-        <v>28103</v>
-      </c>
-      <c r="Q6" t="inlineStr">
+        <v>1245473</v>
+      </c>
+      <c r="AO6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="R6" t="n">
+      <c r="AP6" t="n">
         <v>12.9</v>
       </c>
-      <c r="S6" t="n">
+      <c r="AQ6" t="n">
         <v>12.7</v>
       </c>
-      <c r="T6" t="n">
+      <c r="AR6" t="n">
         <v>12.1</v>
       </c>
-      <c r="U6" t="n">
+      <c r="AS6" t="n">
         <v>12.1</v>
       </c>
-      <c r="V6" t="n">
+      <c r="AT6" t="n">
         <v>12.7</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="5" t="inlineStr">
         <is>
-          <t>Net cash from investing activities</t>
+          <t>Loans and advances at amortised cost to customers</t>
         </is>
       </c>
       <c r="B7" s="5" t="n">
-        <v>2095</v>
+        <v>141750</v>
       </c>
       <c r="C7" s="5" t="n">
-        <v>-9234</v>
+        <v>136047</v>
       </c>
       <c r="D7" s="5" t="n">
-        <v>-18787</v>
-      </c>
-      <c r="E7" s="5" t="n">
-        <v>-8611</v>
-      </c>
-      <c r="F7" s="5" t="n">
-        <v>-1653</v>
-      </c>
+        <v>137177</v>
+      </c>
+      <c r="E7" s="5" t="n"/>
+      <c r="F7" s="5" t="n"/>
       <c r="I7" t="inlineStr">
         <is>
-          <t>Net cash from investing activities</t>
-        </is>
-      </c>
-      <c r="J7" t="n">
-        <v>-1653</v>
-      </c>
-      <c r="K7" t="n">
-        <v>-8611</v>
+          <t>Loans and advances at amortised cost to customers</t>
+        </is>
       </c>
       <c r="L7" t="n">
-        <v>-18787</v>
+        <v>137177</v>
       </c>
       <c r="M7" t="n">
-        <v>-9234</v>
+        <v>136047</v>
       </c>
       <c r="N7" t="n">
-        <v>2095</v>
-      </c>
-      <c r="Q7" t="inlineStr">
+        <v>141750</v>
+      </c>
+      <c r="AO7" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="R7" t="n">
+      <c r="AP7" t="n">
         <v>17.5</v>
       </c>
-      <c r="S7" t="n">
+      <c r="AQ7" t="n">
         <v>16.7</v>
       </c>
-      <c r="T7" t="n">
+      <c r="AR7" t="n">
         <v>16</v>
       </c>
-      <c r="U7" t="n">
+      <c r="AS7" t="n">
         <v>15.1</v>
       </c>
-      <c r="V7" t="n">
+      <c r="AT7" t="n">
         <v>16.1</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="5" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
+          <t>Customer deposits</t>
         </is>
       </c>
       <c r="B8" s="5" t="n">
-        <v>800</v>
+        <v>324358</v>
       </c>
       <c r="C8" s="5" t="n">
-        <v>1931</v>
+        <v>306124</v>
       </c>
       <c r="D8" s="5" t="n">
-        <v>-4009</v>
-      </c>
-      <c r="E8" s="5" t="n">
-        <v>7386</v>
-      </c>
-      <c r="F8" s="5" t="n">
-        <v>1122</v>
-      </c>
+        <v>287200</v>
+      </c>
+      <c r="E8" s="5" t="n"/>
+      <c r="F8" s="5" t="n"/>
       <c r="I8" t="inlineStr">
         <is>
-          <t>Net cash from financing activities</t>
-        </is>
-      </c>
-      <c r="J8" t="n">
-        <v>1122</v>
-      </c>
-      <c r="K8" t="n">
-        <v>7386</v>
+          <t>Customer deposits</t>
+        </is>
       </c>
       <c r="L8" t="n">
-        <v>-4009</v>
+        <v>287200</v>
       </c>
       <c r="M8" t="n">
-        <v>1931</v>
+        <v>306124</v>
       </c>
       <c r="N8" t="n">
-        <v>800</v>
-      </c>
-      <c r="Q8" t="inlineStr">
+        <v>324358</v>
+      </c>
+      <c r="AO8" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="R8" t="n">
+      <c r="AP8" t="n">
         <v>20.5</v>
       </c>
-      <c r="S8" t="n">
+      <c r="AQ8" t="n">
         <v>20.8</v>
       </c>
-      <c r="T8" t="n">
+      <c r="AR8" t="n">
         <v>19.2</v>
       </c>
-      <c r="U8" t="n">
+      <c r="AS8" t="n">
         <v>18.1</v>
       </c>
-      <c r="V8" t="n">
+      <c r="AT8" t="n">
         <v>19</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="5" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="B9" s="5" t="n">
-        <v>229953</v>
+        <v>62313</v>
       </c>
       <c r="C9" s="5" t="n">
-        <v>200695</v>
+        <v>59220</v>
       </c>
       <c r="D9" s="5" t="n">
-        <v>208412</v>
+        <v>60504</v>
       </c>
       <c r="E9" s="5" t="n">
-        <v>219854</v>
+        <v>58953</v>
       </c>
       <c r="F9" s="5" t="n">
-        <v>185860</v>
+        <v>56317</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>Cash and cash equivalents at end of year</t>
+          <t>Total equity</t>
         </is>
       </c>
       <c r="J9" t="n">
-        <v>185860</v>
+        <v>56317</v>
       </c>
       <c r="K9" t="n">
-        <v>219854</v>
+        <v>58953</v>
       </c>
       <c r="L9" t="n">
-        <v>208412</v>
+        <v>60504</v>
       </c>
       <c r="M9" t="n">
-        <v>200695</v>
+        <v>59220</v>
       </c>
       <c r="N9" t="n">
-        <v>229953</v>
-      </c>
-      <c r="Q9" t="inlineStr">
+        <v>62313</v>
+      </c>
+      <c r="AO9" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="R9" t="n">
+      <c r="AP9" t="n">
         <v>3.7</v>
       </c>
-      <c r="S9" t="n">
+      <c r="AQ9" t="n">
         <v>4.6</v>
       </c>
-      <c r="T9" t="n">
+      <c r="AR9" t="n">
         <v>6</v>
       </c>
-      <c r="U9" t="n">
+      <c r="AS9" t="n">
         <v>5.8</v>
       </c>
-      <c r="V9" t="n">
+      <c r="AT9" t="n">
         <v>5.8</v>
       </c>
     </row>
     <row r="10">
-      <c r="Q10" t="inlineStr">
+      <c r="AO10" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="R10" t="n">
+      <c r="AP10" t="n">
         <v>140</v>
       </c>
-      <c r="S10" t="n">
+      <c r="AQ10" t="n">
         <v>148</v>
       </c>
-      <c r="T10" t="n">
+      <c r="AR10" t="n">
         <v>151</v>
       </c>
-      <c r="U10" t="n">
+      <c r="AS10" t="n">
         <v>147.9</v>
       </c>
-      <c r="V10" t="n">
+      <c r="AT10" t="n">
         <v>149.7</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="3" t="inlineStr">
         <is>
-          <t>Pillar 3 Key Metrics</t>
-        </is>
-      </c>
-      <c r="Q11" t="inlineStr">
+          <t>Profit &amp; Loss Summary (£m)</t>
+        </is>
+      </c>
+      <c r="AO11" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="S11" t="n">
+      <c r="AQ11" t="n">
         <v>108</v>
       </c>
-      <c r="T11" t="n">
+      <c r="AR11" t="n">
         <v>110</v>
       </c>
-      <c r="U11" t="n">
+      <c r="AS11" t="n">
         <v>112</v>
       </c>
-      <c r="V11" t="n">
+      <c r="AT11" t="n">
         <v>113</v>
       </c>
     </row>
@@ -1478,201 +2123,855 @@
           <t>FY2021</t>
         </is>
       </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
     </row>
     <row r="13">
-      <c r="A13" s="6" t="inlineStr">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>20927</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>19037</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>18268</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>18194</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>15408</v>
+      </c>
+      <c r="Q13" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="R13" t="n">
+        <v>15408</v>
+      </c>
+      <c r="S13" t="n">
+        <v>18194</v>
+      </c>
+      <c r="T13" t="n">
+        <v>18268</v>
+      </c>
+      <c r="U13" t="n">
+        <v>19037</v>
+      </c>
+      <c r="V13" t="n">
+        <v>20927</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>-13105</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>-12673</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>-12463</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>-12398</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>-10259</v>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="R14" t="n">
+        <v>-10259</v>
+      </c>
+      <c r="S14" t="n">
+        <v>-12398</v>
+      </c>
+      <c r="T14" t="n">
+        <v>-12463</v>
+      </c>
+      <c r="U14" t="n">
+        <v>-12673</v>
+      </c>
+      <c r="V14" t="n">
+        <v>-13105</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B15" s="5" t="n">
+        <v>4658</v>
+      </c>
+      <c r="C15" s="5" t="n">
+        <v>3748</v>
+      </c>
+      <c r="D15" s="5" t="n">
+        <v>3561</v>
+      </c>
+      <c r="E15" s="5" t="n">
+        <v>4382</v>
+      </c>
+      <c r="F15" s="5" t="n">
+        <v>4588</v>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="R15" t="n">
+        <v>4588</v>
+      </c>
+      <c r="S15" t="n">
+        <v>4382</v>
+      </c>
+      <c r="T15" t="n">
+        <v>3561</v>
+      </c>
+      <c r="U15" t="n">
+        <v>3748</v>
+      </c>
+      <c r="V15" t="n">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="3" t="inlineStr">
+        <is>
+          <t>Statement of Changes in Equity Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B18" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C18" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D18" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E18" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F18" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>59220</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>60504</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>58953</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>56317</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>53710</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>Opening equity</t>
+        </is>
+      </c>
+      <c r="Z19" t="n">
+        <v>53710</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>56317</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>58953</v>
+      </c>
+      <c r="AC19" t="n">
+        <v>60504</v>
+      </c>
+      <c r="AD19" t="n">
+        <v>59220</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="B20" s="5" t="n">
+        <v>5757</v>
+      </c>
+      <c r="C20" s="5" t="n">
+        <v>2508</v>
+      </c>
+      <c r="D20" s="5" t="n">
+        <v>3593</v>
+      </c>
+      <c r="E20" s="5" t="n">
+        <v>1811</v>
+      </c>
+      <c r="F20" s="5" t="n">
+        <v>2903</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>Total comprehensive income</t>
+        </is>
+      </c>
+      <c r="Z20" t="n">
+        <v>2903</v>
+      </c>
+      <c r="AA20" t="n">
+        <v>1811</v>
+      </c>
+      <c r="AB20" t="n">
+        <v>3593</v>
+      </c>
+      <c r="AC20" t="n">
+        <v>2508</v>
+      </c>
+      <c r="AD20" t="n">
+        <v>5757</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Other movements, net</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-2664</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-3792</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-2042</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>825</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-296</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>Other movements, net</t>
+        </is>
+      </c>
+      <c r="Z21" t="n">
+        <v>-296</v>
+      </c>
+      <c r="AA21" t="n">
+        <v>825</v>
+      </c>
+      <c r="AB21" t="n">
+        <v>-2042</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>-3792</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>-2664</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="B22" s="5" t="n">
+        <v>62313</v>
+      </c>
+      <c r="C22" s="5" t="n">
+        <v>59220</v>
+      </c>
+      <c r="D22" s="5" t="n">
+        <v>60504</v>
+      </c>
+      <c r="E22" s="5" t="n">
+        <v>58953</v>
+      </c>
+      <c r="F22" s="5" t="n">
+        <v>56317</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>Closing equity</t>
+        </is>
+      </c>
+      <c r="Z22" t="n">
+        <v>56317</v>
+      </c>
+      <c r="AA22" t="n">
+        <v>58953</v>
+      </c>
+      <c r="AB22" t="n">
+        <v>60504</v>
+      </c>
+      <c r="AC22" t="n">
+        <v>59220</v>
+      </c>
+      <c r="AD22" t="n">
+        <v>62313</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="3" t="inlineStr">
+        <is>
+          <t>Cash Flow Summary (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C25" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D25" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E25" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F25" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AH25" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+      <c r="AI25" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="AJ25" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="AK25" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="AL25" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>28103</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>1991</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>16367</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>24984</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>17497</v>
+      </c>
+      <c r="AG26" t="inlineStr">
+        <is>
+          <t>Net cash from operating activities</t>
+        </is>
+      </c>
+      <c r="AH26" t="n">
+        <v>17497</v>
+      </c>
+      <c r="AI26" t="n">
+        <v>24984</v>
+      </c>
+      <c r="AJ26" t="n">
+        <v>16367</v>
+      </c>
+      <c r="AK26" t="n">
+        <v>1991</v>
+      </c>
+      <c r="AL26" t="n">
+        <v>28103</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="B27" s="5" t="n">
+        <v>2095</v>
+      </c>
+      <c r="C27" s="5" t="n">
+        <v>-9234</v>
+      </c>
+      <c r="D27" s="5" t="n">
+        <v>-18787</v>
+      </c>
+      <c r="E27" s="5" t="n">
+        <v>-8611</v>
+      </c>
+      <c r="F27" s="5" t="n">
+        <v>-1653</v>
+      </c>
+      <c r="AG27" t="inlineStr">
+        <is>
+          <t>Net cash from investing activities</t>
+        </is>
+      </c>
+      <c r="AH27" t="n">
+        <v>-1653</v>
+      </c>
+      <c r="AI27" t="n">
+        <v>-8611</v>
+      </c>
+      <c r="AJ27" t="n">
+        <v>-18787</v>
+      </c>
+      <c r="AK27" t="n">
+        <v>-9234</v>
+      </c>
+      <c r="AL27" t="n">
+        <v>2095</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>800</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>1931</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>-4009</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>7386</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>1122</v>
+      </c>
+      <c r="AG28" t="inlineStr">
+        <is>
+          <t>Net cash from financing activities</t>
+        </is>
+      </c>
+      <c r="AH28" t="n">
+        <v>1122</v>
+      </c>
+      <c r="AI28" t="n">
+        <v>7386</v>
+      </c>
+      <c r="AJ28" t="n">
+        <v>-4009</v>
+      </c>
+      <c r="AK28" t="n">
+        <v>1931</v>
+      </c>
+      <c r="AL28" t="n">
+        <v>800</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="B29" s="5" t="n">
+        <v>229953</v>
+      </c>
+      <c r="C29" s="5" t="n">
+        <v>200695</v>
+      </c>
+      <c r="D29" s="5" t="n">
+        <v>208412</v>
+      </c>
+      <c r="E29" s="5" t="n">
+        <v>219854</v>
+      </c>
+      <c r="F29" s="5" t="n">
+        <v>185860</v>
+      </c>
+      <c r="AG29" t="inlineStr">
+        <is>
+          <t>Cash and cash equivalents at end of year</t>
+        </is>
+      </c>
+      <c r="AH29" t="n">
+        <v>185860</v>
+      </c>
+      <c r="AI29" t="n">
+        <v>219854</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>208412</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>200695</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>229953</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="3" t="inlineStr">
+        <is>
+          <t>Pillar 3 Key Metrics</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C32" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D32" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E32" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F32" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
         <is>
           <t>CET1 Ratio</t>
         </is>
       </c>
-      <c r="B13" s="6" t="inlineStr">
+      <c r="B33" s="6" t="inlineStr">
         <is>
           <t>12.7%</t>
         </is>
       </c>
-      <c r="C13" s="6" t="inlineStr">
+      <c r="C33" s="6" t="inlineStr">
         <is>
           <t>12.1%</t>
         </is>
       </c>
-      <c r="D13" s="6" t="inlineStr">
+      <c r="D33" s="6" t="inlineStr">
         <is>
           <t>12.1%</t>
         </is>
       </c>
-      <c r="E13" s="6" t="inlineStr">
+      <c r="E33" s="6" t="inlineStr">
         <is>
           <t>12.7%</t>
         </is>
       </c>
-      <c r="F13" s="6" t="inlineStr">
+      <c r="F33" s="6" t="inlineStr">
         <is>
           <t>12.9%</t>
         </is>
       </c>
     </row>
-    <row r="14">
-      <c r="A14" s="6" t="inlineStr">
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
         <is>
           <t>Tier 1 Ratio</t>
         </is>
       </c>
-      <c r="B14" s="6" t="inlineStr">
+      <c r="B34" s="6" t="inlineStr">
         <is>
           <t>16.1%</t>
         </is>
       </c>
-      <c r="C14" s="6" t="inlineStr">
+      <c r="C34" s="6" t="inlineStr">
         <is>
           <t>15.1%</t>
         </is>
       </c>
-      <c r="D14" s="6" t="inlineStr">
+      <c r="D34" s="6" t="inlineStr">
         <is>
           <t>16.0%</t>
         </is>
       </c>
-      <c r="E14" s="6" t="inlineStr">
+      <c r="E34" s="6" t="inlineStr">
         <is>
           <t>16.7%</t>
         </is>
       </c>
-      <c r="F14" s="6" t="inlineStr">
+      <c r="F34" s="6" t="inlineStr">
         <is>
           <t>17.5%</t>
         </is>
       </c>
     </row>
-    <row r="15">
-      <c r="A15" s="6" t="inlineStr">
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
         <is>
           <t>Total Capital Ratio</t>
         </is>
       </c>
-      <c r="B15" s="6" t="inlineStr">
+      <c r="B35" s="6" t="inlineStr">
         <is>
           <t>19.0%</t>
         </is>
       </c>
-      <c r="C15" s="6" t="inlineStr">
+      <c r="C35" s="6" t="inlineStr">
         <is>
           <t>18.1%</t>
         </is>
       </c>
-      <c r="D15" s="6" t="inlineStr">
+      <c r="D35" s="6" t="inlineStr">
         <is>
           <t>19.2%</t>
         </is>
       </c>
-      <c r="E15" s="6" t="inlineStr">
+      <c r="E35" s="6" t="inlineStr">
         <is>
           <t>20.8%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="inlineStr">
+      <c r="F35" s="6" t="inlineStr">
         <is>
           <t>20.5%</t>
         </is>
       </c>
     </row>
-    <row r="16">
-      <c r="A16" s="6" t="inlineStr">
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
         <is>
           <t>Leverage Ratio</t>
         </is>
       </c>
-      <c r="B16" s="6" t="inlineStr">
+      <c r="B36" s="6" t="inlineStr">
         <is>
           <t>5.8%</t>
         </is>
       </c>
-      <c r="C16" s="6" t="inlineStr">
+      <c r="C36" s="6" t="inlineStr">
         <is>
           <t>5.8%</t>
         </is>
       </c>
-      <c r="D16" s="6" t="inlineStr">
+      <c r="D36" s="6" t="inlineStr">
         <is>
           <t>6.0%</t>
         </is>
       </c>
-      <c r="E16" s="6" t="inlineStr">
+      <c r="E36" s="6" t="inlineStr">
         <is>
           <t>4.6%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="inlineStr">
+      <c r="F36" s="6" t="inlineStr">
         <is>
           <t>3.7%</t>
         </is>
       </c>
     </row>
-    <row r="17">
-      <c r="A17" s="6" t="inlineStr">
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
         <is>
           <t>LCR</t>
         </is>
       </c>
-      <c r="B17" s="6" t="inlineStr">
+      <c r="B37" s="6" t="inlineStr">
         <is>
           <t>149.7%</t>
         </is>
       </c>
-      <c r="C17" s="6" t="inlineStr">
+      <c r="C37" s="6" t="inlineStr">
         <is>
           <t>147.9%</t>
         </is>
       </c>
-      <c r="D17" s="6" t="inlineStr">
+      <c r="D37" s="6" t="inlineStr">
         <is>
           <t>151%</t>
         </is>
       </c>
-      <c r="E17" s="6" t="inlineStr">
+      <c r="E37" s="6" t="inlineStr">
         <is>
           <t>148%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="inlineStr">
+      <c r="F37" s="6" t="inlineStr">
         <is>
           <t>140%</t>
         </is>
       </c>
     </row>
-    <row r="18">
-      <c r="A18" s="6" t="inlineStr">
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
         <is>
           <t>NSFR</t>
         </is>
       </c>
-      <c r="B18" s="6" t="inlineStr">
+      <c r="B38" s="6" t="inlineStr">
         <is>
           <t>113%</t>
         </is>
       </c>
-      <c r="C18" s="6" t="inlineStr">
+      <c r="C38" s="6" t="inlineStr">
         <is>
           <t>112%</t>
         </is>
       </c>
-      <c r="D18" s="6" t="inlineStr">
+      <c r="D38" s="6" t="inlineStr">
         <is>
           <t>110%</t>
         </is>
       </c>
-      <c r="E18" s="6" t="inlineStr">
+      <c r="E38" s="6" t="inlineStr">
         <is>
           <t>108%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="inlineStr">
+      <c r="F38" s="6" t="inlineStr">
         <is>
           <t>Not publicly disclosed</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="45" customHeight="1">
-      <c r="A20" s="7" t="inlineStr">
+    <row r="40" ht="45" customHeight="1">
+      <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2021 capital figures are restated (Over-issuance of Securities matter). Leverage ratio basis changes year-on-year (see Leverage Ratio sheet).</t>
         </is>
@@ -1680,7 +2979,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A40:F40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
@@ -1688,6 +2987,581 @@
 </file>
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Tier 1 Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Tier 1 (T1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Total Capital</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>42129</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>40444</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>40530</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>42321</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>37954</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Total Capital Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis, % of RWA</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total regulatory capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk weighted assets (RWAs)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>222247</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>223648</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>211193</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>203833</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>185467</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F6"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — RWA Breakdown</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>RWA category breakdown</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not publicly disclosed</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="150" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC's own 'Capital risk' section of the Risk review (see p3_sources() URLs above):
+NOT PUBLICLY DISCLOSED within the Annual Report: the Capital risk section (p.231 of the FY2025 Annual Report) discloses only the single aggregate Total RWAs figure and capital ratios, not a UK OV1-style breakdown by credit/counterparty credit/market/operational risk - confirmed by reading that section in full. The Annual Report itself references a separate, standalone 'Barclays Bank PLC 2025 Pillar 3 Report' as the source for further risk-profile detail, but that document was not sourced within this batch's reviewed pages.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A6:F6"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1852,7 +3726,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -1995,7 +3869,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2152,7 +4026,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -2275,6 +4149,3446 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F51"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="70" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Balance Sheet</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC Group (consolidated basis), £m. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Assets</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Cash and balances at central banks</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>208544</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>180365</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>189686</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>202142</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>169085</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Cash collateral and settlement balances</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>124519</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>113987</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>103708</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>107862</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>88085</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities at amortised cost</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>55153</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>50227</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>39046</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost to banks</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>9036</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>8780</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>9024</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost to customers</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>141750</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>136047</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>137177</v>
+      </c>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost (total, FY2022/FY2021 basis)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n"/>
+      <c r="E10" s="6" t="n">
+        <v>182507</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>145259</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Reverse repurchase agreements and other similar secured lending</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>17662</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>3393</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>1103</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>725</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>3177</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Trading portfolio assets</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>189743</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>166244</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>174566</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>133771</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>146871</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through the income statement</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>185002</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>191845</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>204236</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>211128</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>188226</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n">
+        <v>252192</v>
+      </c>
+      <c r="C14" s="6" t="n">
+        <v>292356</v>
+      </c>
+      <c r="D14" s="6" t="n">
+        <v>256111</v>
+      </c>
+      <c r="E14" s="6" t="n">
+        <v>302976</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>262291</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Financial assets at fair value through other comprehensive income</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n">
+        <v>42818</v>
+      </c>
+      <c r="C15" s="6" t="n">
+        <v>51010</v>
+      </c>
+      <c r="D15" s="6" t="n">
+        <v>51423</v>
+      </c>
+      <c r="E15" s="6" t="n">
+        <v>45084</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>45908</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Investments in associates and joint ventures</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>22</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>26</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Goodwill and intangible assets</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>1303</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>1425</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>1084</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>1665</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>1449</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Property, plant and equipment</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>1603</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>1546</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>1262</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>1379</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1248</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>Current tax assets</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>376</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>785</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>546</v>
+      </c>
+      <c r="E19" s="6" t="n">
+        <v>737</v>
+      </c>
+      <c r="F19" s="6" t="n">
+        <v>589</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax assets</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>2936</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>4133</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>3888</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>4583</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>2981</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit assets</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n">
+        <v>3240</v>
+      </c>
+      <c r="C21" s="6" t="n">
+        <v>3263</v>
+      </c>
+      <c r="D21" s="6" t="n">
+        <v>3667</v>
+      </c>
+      <c r="E21" s="6" t="n">
+        <v>4743</v>
+      </c>
+      <c r="F21" s="6" t="n">
+        <v>3879</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Assets included in disposal group classified as held for sale</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>5932</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>9854</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>3916</v>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Other assets</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>3650</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>3250</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>4701</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>4209</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>2706</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Total assets</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>1245473</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>1218524</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>1185166</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>1203537</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>1061778</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>Liabilities</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n"/>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="6" t="inlineStr">
+        <is>
+          <t>Deposits at amortised cost from banks</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n">
+        <v>20393</v>
+      </c>
+      <c r="C26" s="6" t="n">
+        <v>13252</v>
+      </c>
+      <c r="D26" s="6" t="n">
+        <v>14598</v>
+      </c>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Deposits at amortised cost from customers</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>324358</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>306124</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>287200</v>
+      </c>
+      <c r="E27" s="6" t="n"/>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Deposits at amortised cost (total, FY2022/FY2021 basis)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n"/>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n">
+        <v>291579</v>
+      </c>
+      <c r="F28" s="6" t="n">
+        <v>262828</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Cash collateral and settlement balances (liabilities)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n">
+        <v>116811</v>
+      </c>
+      <c r="C29" s="6" t="n">
+        <v>104627</v>
+      </c>
+      <c r="D29" s="6" t="n">
+        <v>92988</v>
+      </c>
+      <c r="E29" s="6" t="n">
+        <v>96811</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>79047</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Repurchase agreements and other similar secured borrowing</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>18651</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>29397</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>28554</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>11965</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>12769</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Debt securities in issue</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>57229</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>35803</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>45653</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>60012</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>48388</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Subordinated liabilities</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>45239</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>41875</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>35903</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>38253</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>32185</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Trading portfolio liabilities</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>56829</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>56182</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>57761</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>72460</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>53291</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Financial liabilities designated at fair value</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>293527</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>279777</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>298573</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>272055</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>251131</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Derivative financial instruments (liabilities)</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>240757</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>279331</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>249880</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>289206</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>256523</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>Current tax liabilities</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>611</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>404</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>411</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>422</v>
+      </c>
+      <c r="F36" s="6" t="n">
+        <v>688</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Deferred tax liabilities</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit liabilities</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>157</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>164</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>173</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>184</v>
+      </c>
+      <c r="F38" s="6" t="n">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Liabilities included in disposal group classified as held for sale</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>3726</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>3164</v>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Provisions</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n">
+        <v>766</v>
+      </c>
+      <c r="C40" s="6" t="n">
+        <v>736</v>
+      </c>
+      <c r="D40" s="6" t="n">
+        <v>817</v>
+      </c>
+      <c r="E40" s="6" t="n">
+        <v>858</v>
+      </c>
+      <c r="F40" s="6" t="n">
+        <v>1110</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Other liabilities</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>7831</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>7904</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>8984</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>10779</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>7249</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="n">
+        <v>1183160</v>
+      </c>
+      <c r="C42" s="5" t="n">
+        <v>1159304</v>
+      </c>
+      <c r="D42" s="5" t="n">
+        <v>1124662</v>
+      </c>
+      <c r="E42" s="5" t="n">
+        <v>1144584</v>
+      </c>
+      <c r="F42" s="5" t="n">
+        <v>1005461</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Equity</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n"/>
+      <c r="C43" s="6" t="n"/>
+      <c r="D43" s="6" t="n"/>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Called up share capital and share premium</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n">
+        <v>2346</v>
+      </c>
+      <c r="C44" s="6" t="n">
+        <v>2348</v>
+      </c>
+      <c r="D44" s="6" t="n">
+        <v>2348</v>
+      </c>
+      <c r="E44" s="6" t="n">
+        <v>2348</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>2348</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n">
+        <v>10446</v>
+      </c>
+      <c r="C45" s="6" t="n">
+        <v>9604</v>
+      </c>
+      <c r="D45" s="6" t="n">
+        <v>10765</v>
+      </c>
+      <c r="E45" s="6" t="n">
+        <v>10691</v>
+      </c>
+      <c r="F45" s="6" t="n">
+        <v>9693</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>-179</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>-363</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>-1464</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>861</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>49700</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>48570</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>47754</v>
+      </c>
+      <c r="E47" s="6" t="n">
+        <v>47378</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>43415</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="5" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+      <c r="B48" s="5" t="n">
+        <v>62313</v>
+      </c>
+      <c r="C48" s="5" t="n">
+        <v>59220</v>
+      </c>
+      <c r="D48" s="5" t="n">
+        <v>60504</v>
+      </c>
+      <c r="E48" s="5" t="n">
+        <v>58953</v>
+      </c>
+      <c r="F48" s="5" t="n">
+        <v>56317</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="5" t="inlineStr">
+        <is>
+          <t>Total liabilities and equity</t>
+        </is>
+      </c>
+      <c r="B49" s="5" t="n">
+        <v>1245473</v>
+      </c>
+      <c r="C49" s="5" t="n">
+        <v>1218524</v>
+      </c>
+      <c r="D49" s="5" t="n">
+        <v>1185166</v>
+      </c>
+      <c r="E49" s="5" t="n">
+        <v>1203537</v>
+      </c>
+      <c r="F49" s="5" t="n">
+        <v>1061778</v>
+      </c>
+    </row>
+    <row r="51" ht="220" customHeight="1">
+      <c r="A51" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC consolidated financial statements ("Barclays Bank Group"), £m, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.284-289 (Consolidated income statement / statement of comprehensive income / balance sheet / statement of changes in equity) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 balance sheet &amp; equity comparative: Barclays Bank PLC Annual Report 2024, p.268-271 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021 (restated): Barclays Bank PLC Annual Report 2022, p.166-170 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
+Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) was not sourced within this batch's reviewed pages of the FY2022 Annual Report - only that year's Profit after tax and Total comprehensive income (from the Statement of Changes in Equity) are populated; the underlying OCI note itself was not reviewed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A51:F51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F48"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="72" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Profit &amp; Loss</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC Group (consolidated basis), £m. See source note at bottom.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Line item</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025 (£m)</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024 (£m)</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023 (£m)</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022 (£m)</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021 (£m)</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Income</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Interest and similar income</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>23409</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>25780</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>24261</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>11779</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>5672</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Interest and similar expense</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>-16115</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>-19035</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>-17608</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>-6381</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>-2599</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="5" t="inlineStr">
+        <is>
+          <t>Net interest income</t>
+        </is>
+      </c>
+      <c r="B7" s="5" t="n">
+        <v>7294</v>
+      </c>
+      <c r="C7" s="5" t="n">
+        <v>6745</v>
+      </c>
+      <c r="D7" s="5" t="n">
+        <v>6653</v>
+      </c>
+      <c r="E7" s="5" t="n">
+        <v>5398</v>
+      </c>
+      <c r="F7" s="5" t="n">
+        <v>3073</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission income</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>9879</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>9486</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>8708</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>8171</v>
+      </c>
+      <c r="F8" s="6" t="n">
+        <v>8581</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Fee and commission expense</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>-3326</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>-3215</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>-3247</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>-2745</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>-1994</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="5" t="inlineStr">
+        <is>
+          <t>Net fee and commission income</t>
+        </is>
+      </c>
+      <c r="B10" s="5" t="n">
+        <v>6553</v>
+      </c>
+      <c r="C10" s="5" t="n">
+        <v>6271</v>
+      </c>
+      <c r="D10" s="5" t="n">
+        <v>5461</v>
+      </c>
+      <c r="E10" s="5" t="n">
+        <v>5426</v>
+      </c>
+      <c r="F10" s="5" t="n">
+        <v>6587</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Net trading income</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>7104</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>5900</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>5980</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>7624</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>5788</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Net investment income/(expense)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>-72</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>112</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>-323</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>-80</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Other income</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n">
+        <v>48</v>
+      </c>
+      <c r="C13" s="6" t="n">
+        <v>52</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>62</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>69</v>
+      </c>
+      <c r="F13" s="6" t="n">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Total income</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>20927</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>19037</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>18268</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>18194</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>15408</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Operating expenses</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Staff costs</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>-5585</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>-5556</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>-5591</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>-5192</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-4456</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Infrastructure costs</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>-816</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>-795</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>-1073</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>-900</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-1054</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Administration and general expenses</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n">
+        <v>-6192</v>
+      </c>
+      <c r="C18" s="6" t="n">
+        <v>-5894</v>
+      </c>
+      <c r="D18" s="6" t="n">
+        <v>-5606</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-4879</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>-4375</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>UK regulatory levies</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="n">
+        <v>-228</v>
+      </c>
+      <c r="C19" s="6" t="n">
+        <v>-242</v>
+      </c>
+      <c r="D19" s="6" t="n">
+        <v>-149</v>
+      </c>
+      <c r="E19" s="6" t="n"/>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Litigation and conduct</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n">
+        <v>-284</v>
+      </c>
+      <c r="C20" s="6" t="n">
+        <v>-186</v>
+      </c>
+      <c r="D20" s="6" t="n">
+        <v>-44</v>
+      </c>
+      <c r="E20" s="6" t="n">
+        <v>-1427</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>-374</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Total operating expenses</t>
+        </is>
+      </c>
+      <c r="B21" s="5" t="n">
+        <v>-13105</v>
+      </c>
+      <c r="C21" s="5" t="n">
+        <v>-12673</v>
+      </c>
+      <c r="D21" s="5" t="n">
+        <v>-12463</v>
+      </c>
+      <c r="E21" s="5" t="n">
+        <v>-12398</v>
+      </c>
+      <c r="F21" s="5" t="n">
+        <v>-10259</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Share of post-tax results of associates and joint ventures</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="C22" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D22" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="E22" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F22" s="6" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Profit/(loss) on disposal of subsidiaries, associates and joint ventures</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="C23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="D23" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="E23" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="F23" s="6" t="n">
+        <v>-12</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="5" t="inlineStr">
+        <is>
+          <t>Profit before impairment</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n">
+        <v>7809</v>
+      </c>
+      <c r="C24" s="5" t="n">
+        <v>6364</v>
+      </c>
+      <c r="D24" s="5" t="n">
+        <v>5801</v>
+      </c>
+      <c r="E24" s="5" t="n">
+        <v>5800</v>
+      </c>
+      <c r="F24" s="5" t="n">
+        <v>5141</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Credit impairment (charges)/releases</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n">
+        <v>-1866</v>
+      </c>
+      <c r="C25" s="6" t="n">
+        <v>-1617</v>
+      </c>
+      <c r="D25" s="6" t="n">
+        <v>-1578</v>
+      </c>
+      <c r="E25" s="6" t="n">
+        <v>-933</v>
+      </c>
+      <c r="F25" s="6" t="n">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Profit before tax</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n">
+        <v>5943</v>
+      </c>
+      <c r="C26" s="5" t="n">
+        <v>4747</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>4223</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>4867</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>5418</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Taxation</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n">
+        <v>-1285</v>
+      </c>
+      <c r="C27" s="6" t="n">
+        <v>-999</v>
+      </c>
+      <c r="D27" s="6" t="n">
+        <v>-662</v>
+      </c>
+      <c r="E27" s="6" t="n">
+        <v>-485</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>-830</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B28" s="5" t="n">
+        <v>4658</v>
+      </c>
+      <c r="C28" s="5" t="n">
+        <v>3748</v>
+      </c>
+      <c r="D28" s="5" t="n">
+        <v>3561</v>
+      </c>
+      <c r="E28" s="5" t="n">
+        <v>4382</v>
+      </c>
+      <c r="F28" s="5" t="n">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n"/>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation differences</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n">
+        <v>-1107</v>
+      </c>
+      <c r="C30" s="6" t="n">
+        <v>-143</v>
+      </c>
+      <c r="D30" s="6" t="n">
+        <v>-1242</v>
+      </c>
+      <c r="E30" s="6" t="n">
+        <v>2411</v>
+      </c>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation tax</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n">
+        <v>-49</v>
+      </c>
+      <c r="C31" s="6" t="n">
+        <v>50</v>
+      </c>
+      <c r="D31" s="6" t="n">
+        <v>33</v>
+      </c>
+      <c r="E31" s="6" t="n">
+        <v>0</v>
+      </c>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>FVOCI debt securities: net gains/(losses) from changes in fair value</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n">
+        <v>695</v>
+      </c>
+      <c r="C32" s="6" t="n">
+        <v>-840</v>
+      </c>
+      <c r="D32" s="6" t="n">
+        <v>1142</v>
+      </c>
+      <c r="E32" s="6" t="n">
+        <v>-6376</v>
+      </c>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>FVOCI debt securities: net losses/(gains) transferred to net profit on disposal</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>201</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>-134</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>-102</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>68</v>
+      </c>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>FVOCI debt securities: net (gains)/losses related to (releases of) impairment</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n">
+        <v>-3</v>
+      </c>
+      <c r="C34" s="6" t="n">
+        <v>1</v>
+      </c>
+      <c r="D34" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="E34" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>FVOCI debt securities: net gains/(losses) due to fair value hedging</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n">
+        <v>30</v>
+      </c>
+      <c r="C35" s="6" t="n">
+        <v>318</v>
+      </c>
+      <c r="D35" s="6" t="n">
+        <v>-849</v>
+      </c>
+      <c r="E35" s="6" t="n">
+        <v>4627</v>
+      </c>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>FVOCI debt securities: tax</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="n">
+        <v>-256</v>
+      </c>
+      <c r="C36" s="6" t="n">
+        <v>181</v>
+      </c>
+      <c r="D36" s="6" t="n">
+        <v>-54</v>
+      </c>
+      <c r="E36" s="6" t="n">
+        <v>449</v>
+      </c>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedging reserve: net gains/(losses) from changes in fair value</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n">
+        <v>2654</v>
+      </c>
+      <c r="C37" s="6" t="n">
+        <v>-1349</v>
+      </c>
+      <c r="D37" s="6" t="n">
+        <v>2506</v>
+      </c>
+      <c r="E37" s="6" t="n">
+        <v>-7290</v>
+      </c>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedging reserve: net (gains)/losses transferred to net profit</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n">
+        <v>-506</v>
+      </c>
+      <c r="C38" s="6" t="n">
+        <v>1950</v>
+      </c>
+      <c r="D38" s="6" t="n">
+        <v>1158</v>
+      </c>
+      <c r="E38" s="6" t="n">
+        <v>543</v>
+      </c>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedging reserve: tax</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n">
+        <v>-607</v>
+      </c>
+      <c r="C39" s="6" t="n">
+        <v>-154</v>
+      </c>
+      <c r="D39" s="6" t="n">
+        <v>-1002</v>
+      </c>
+      <c r="E39" s="6" t="n">
+        <v>1808</v>
+      </c>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss) that may be recycled to profit or loss</t>
+        </is>
+      </c>
+      <c r="B40" s="5" t="n">
+        <v>1052</v>
+      </c>
+      <c r="C40" s="5" t="n">
+        <v>-120</v>
+      </c>
+      <c r="D40" s="5" t="n">
+        <v>1588</v>
+      </c>
+      <c r="E40" s="5" t="n">
+        <v>-3752</v>
+      </c>
+      <c r="F40" s="5" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit remeasurements</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>-419</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>-1182</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>-755</v>
+      </c>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Own credit</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n">
+        <v>89</v>
+      </c>
+      <c r="C42" s="6" t="n">
+        <v>-1131</v>
+      </c>
+      <c r="D42" s="6" t="n">
+        <v>-983</v>
+      </c>
+      <c r="E42" s="6" t="n">
+        <v>2092</v>
+      </c>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>Own credit / retirement benefit tax</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="n">
+        <v>-29</v>
+      </c>
+      <c r="C43" s="6" t="n">
+        <v>430</v>
+      </c>
+      <c r="D43" s="6" t="n">
+        <v>609</v>
+      </c>
+      <c r="E43" s="6" t="n">
+        <v>-156</v>
+      </c>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss) not recycled to profit or loss</t>
+        </is>
+      </c>
+      <c r="B44" s="5" t="n">
+        <v>47</v>
+      </c>
+      <c r="C44" s="5" t="n">
+        <v>-1120</v>
+      </c>
+      <c r="D44" s="5" t="n">
+        <v>-1556</v>
+      </c>
+      <c r="E44" s="5" t="n">
+        <v>1181</v>
+      </c>
+      <c r="F44" s="5" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Other comprehensive income/(loss) for the year</t>
+        </is>
+      </c>
+      <c r="B45" s="5" t="n">
+        <v>1099</v>
+      </c>
+      <c r="C45" s="5" t="n">
+        <v>-1240</v>
+      </c>
+      <c r="D45" s="5" t="n">
+        <v>32</v>
+      </c>
+      <c r="E45" s="5" t="n">
+        <v>-2571</v>
+      </c>
+      <c r="F45" s="5" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year, net of tax</t>
+        </is>
+      </c>
+      <c r="B46" s="5" t="n">
+        <v>5757</v>
+      </c>
+      <c r="C46" s="5" t="n">
+        <v>2508</v>
+      </c>
+      <c r="D46" s="5" t="n">
+        <v>3593</v>
+      </c>
+      <c r="E46" s="5" t="n">
+        <v>1811</v>
+      </c>
+      <c r="F46" s="5" t="n">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="48" ht="220" customHeight="1">
+      <c r="A48" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC consolidated financial statements ("Barclays Bank Group"), £m, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.284-289 (Consolidated income statement / statement of comprehensive income / balance sheet / statement of changes in equity) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 balance sheet &amp; equity comparative: Barclays Bank PLC Annual Report 2024, p.268-271 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021 (restated): Barclays Bank PLC Annual Report 2022, p.166-170 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
+Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) was not sourced within this batch's reviewed pages of the FY2022 Annual Report - only that year's Profit after tax and Total comprehensive income (from the Statement of Changes in Equity) are populated; the underlying OCI note itself was not reviewed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A48:F48"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F85"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="58" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Statement of Changes in Equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC Group (consolidated basis), £m, chronological, 1 January 2021 - 31 December 2025</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Movement</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>Called up share capital and share premium</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>Other equity instruments</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>Other reserves</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>Retained earnings</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>Total equity</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Balance as at 1 January 2021</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>8621</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>3183</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>39558</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>53710</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n"/>
+      <c r="C5" s="6" t="n">
+        <v>631</v>
+      </c>
+      <c r="D5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>3957</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>4588</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation movements</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n"/>
+      <c r="D6" s="6" t="n">
+        <v>-155</v>
+      </c>
+      <c r="E6" s="6" t="n"/>
+      <c r="F6" s="6" t="n">
+        <v>-155</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n"/>
+      <c r="C7" s="6" t="n"/>
+      <c r="D7" s="6" t="n">
+        <v>-362</v>
+      </c>
+      <c r="E7" s="6" t="n"/>
+      <c r="F7" s="6" t="n">
+        <v>-362</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n"/>
+      <c r="D8" s="6" t="n">
+        <v>-1799</v>
+      </c>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n">
+        <v>-1799</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit remeasurement</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n">
+        <v>644</v>
+      </c>
+      <c r="F9" s="6" t="n">
+        <v>644</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Own credit reserve</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n"/>
+      <c r="D10" s="6" t="n">
+        <v>-13</v>
+      </c>
+      <c r="E10" s="6" t="n"/>
+      <c r="F10" s="6" t="n">
+        <v>-13</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n"/>
+      <c r="C11" s="5" t="n">
+        <v>631</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>-2329</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>4601</v>
+      </c>
+      <c r="F11" s="5" t="n">
+        <v>2903</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity instruments</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n">
+        <v>1072</v>
+      </c>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>1075</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>-631</v>
+      </c>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>-631</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n">
+        <v>436</v>
+      </c>
+      <c r="F14" s="6" t="n">
+        <v>436</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share-based payment schemes</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n">
+        <v>-356</v>
+      </c>
+      <c r="F15" s="6" t="n">
+        <v>-356</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on ordinary shares</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n">
+        <v>-794</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>-794</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on preference shares and other shareholders equity</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n">
+        <v>-27</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>-27</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="E18" s="6" t="n">
+        <v>-6</v>
+      </c>
+      <c r="F18" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2021</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C19" s="5" t="n">
+        <v>9693</v>
+      </c>
+      <c r="D19" s="5" t="n">
+        <v>861</v>
+      </c>
+      <c r="E19" s="5" t="n">
+        <v>43415</v>
+      </c>
+      <c r="F19" s="5" t="n">
+        <v>56317</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="n">
+        <v>732</v>
+      </c>
+      <c r="D20" s="6" t="n"/>
+      <c r="E20" s="6" t="n">
+        <v>3650</v>
+      </c>
+      <c r="F20" s="6" t="n">
+        <v>4382</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation movements</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n">
+        <v>2411</v>
+      </c>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n">
+        <v>2411</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="n"/>
+      <c r="C22" s="6" t="n"/>
+      <c r="D22" s="6" t="n">
+        <v>-1224</v>
+      </c>
+      <c r="E22" s="6" t="n"/>
+      <c r="F22" s="6" t="n">
+        <v>-1224</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="n"/>
+      <c r="C23" s="6" t="n"/>
+      <c r="D23" s="6" t="n">
+        <v>-4939</v>
+      </c>
+      <c r="E23" s="6" t="n"/>
+      <c r="F23" s="6" t="n">
+        <v>-4939</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit remeasurement</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="n"/>
+      <c r="C24" s="6" t="n"/>
+      <c r="D24" s="6" t="n"/>
+      <c r="E24" s="6" t="n">
+        <v>-282</v>
+      </c>
+      <c r="F24" s="6" t="n">
+        <v>-282</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>Own credit reserve</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="n"/>
+      <c r="C25" s="6" t="n"/>
+      <c r="D25" s="6" t="n">
+        <v>1463</v>
+      </c>
+      <c r="E25" s="6" t="n"/>
+      <c r="F25" s="6" t="n">
+        <v>1463</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n">
+        <v>732</v>
+      </c>
+      <c r="D26" s="5" t="n">
+        <v>-2289</v>
+      </c>
+      <c r="E26" s="5" t="n">
+        <v>3368</v>
+      </c>
+      <c r="F26" s="5" t="n">
+        <v>1811</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity instruments</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="n"/>
+      <c r="C27" s="6" t="n">
+        <v>998</v>
+      </c>
+      <c r="D27" s="6" t="n"/>
+      <c r="E27" s="6" t="n">
+        <v>38</v>
+      </c>
+      <c r="F27" s="6" t="n">
+        <v>1036</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="n"/>
+      <c r="C28" s="6" t="n">
+        <v>-732</v>
+      </c>
+      <c r="D28" s="6" t="n"/>
+      <c r="E28" s="6" t="n"/>
+      <c r="F28" s="6" t="n">
+        <v>-732</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>Employee share schemes</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="n"/>
+      <c r="C29" s="6" t="n"/>
+      <c r="D29" s="6" t="n"/>
+      <c r="E29" s="6" t="n">
+        <v>419</v>
+      </c>
+      <c r="F29" s="6" t="n">
+        <v>419</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share-based payment schemes</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="n"/>
+      <c r="C30" s="6" t="n"/>
+      <c r="D30" s="6" t="n"/>
+      <c r="E30" s="6" t="n">
+        <v>-413</v>
+      </c>
+      <c r="F30" s="6" t="n">
+        <v>-413</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on ordinary shares</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="n"/>
+      <c r="C31" s="6" t="n"/>
+      <c r="D31" s="6" t="n"/>
+      <c r="E31" s="6" t="n">
+        <v>-200</v>
+      </c>
+      <c r="F31" s="6" t="n">
+        <v>-200</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on preference shares and other shareholders equity</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n">
+        <v>-31</v>
+      </c>
+      <c r="F32" s="6" t="n">
+        <v>-31</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>Own credit realisation</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n"/>
+      <c r="C33" s="6" t="n"/>
+      <c r="D33" s="6" t="n">
+        <v>-36</v>
+      </c>
+      <c r="E33" s="6" t="n">
+        <v>36</v>
+      </c>
+      <c r="F33" s="6" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>Capital contribution from Barclays PLC</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="n"/>
+      <c r="C34" s="6" t="n"/>
+      <c r="D34" s="6" t="n"/>
+      <c r="E34" s="6" t="n">
+        <v>750</v>
+      </c>
+      <c r="F34" s="6" t="n">
+        <v>750</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="n"/>
+      <c r="C35" s="6" t="n"/>
+      <c r="D35" s="6" t="n"/>
+      <c r="E35" s="6" t="n">
+        <v>-4</v>
+      </c>
+      <c r="F35" s="6" t="n">
+        <v>-4</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2022</t>
+        </is>
+      </c>
+      <c r="B36" s="5" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C36" s="5" t="n">
+        <v>10691</v>
+      </c>
+      <c r="D36" s="5" t="n">
+        <v>-1464</v>
+      </c>
+      <c r="E36" s="5" t="n">
+        <v>47378</v>
+      </c>
+      <c r="F36" s="5" t="n">
+        <v>58953</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="n"/>
+      <c r="C37" s="6" t="n">
+        <v>808</v>
+      </c>
+      <c r="D37" s="6" t="n"/>
+      <c r="E37" s="6" t="n">
+        <v>2753</v>
+      </c>
+      <c r="F37" s="6" t="n">
+        <v>3561</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation movements</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="n"/>
+      <c r="C38" s="6" t="n"/>
+      <c r="D38" s="6" t="n">
+        <v>-1209</v>
+      </c>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n">
+        <v>-1209</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="n"/>
+      <c r="C39" s="6" t="n"/>
+      <c r="D39" s="6" t="n">
+        <v>135</v>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n">
+        <v>2662</v>
+      </c>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n">
+        <v>2662</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit remeasurement</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n"/>
+      <c r="C41" s="6" t="n"/>
+      <c r="D41" s="6" t="n"/>
+      <c r="E41" s="6" t="n">
+        <v>-846</v>
+      </c>
+      <c r="F41" s="6" t="n">
+        <v>-846</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>Own credit reserve</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="n"/>
+      <c r="C42" s="6" t="n"/>
+      <c r="D42" s="6" t="n">
+        <v>-710</v>
+      </c>
+      <c r="E42" s="6" t="n"/>
+      <c r="F42" s="6" t="n">
+        <v>-710</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B43" s="5" t="n"/>
+      <c r="C43" s="5" t="n">
+        <v>808</v>
+      </c>
+      <c r="D43" s="5" t="n">
+        <v>878</v>
+      </c>
+      <c r="E43" s="5" t="n">
+        <v>1907</v>
+      </c>
+      <c r="F43" s="5" t="n">
+        <v>3593</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity instruments</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="n"/>
+      <c r="C44" s="6" t="n">
+        <v>74</v>
+      </c>
+      <c r="D44" s="6" t="n"/>
+      <c r="E44" s="6" t="n">
+        <v>-12</v>
+      </c>
+      <c r="F44" s="6" t="n">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n">
+        <v>-808</v>
+      </c>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n">
+        <v>-808</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>Employee settled Barclays PLC share schemes</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n"/>
+      <c r="C46" s="6" t="n"/>
+      <c r="D46" s="6" t="n"/>
+      <c r="E46" s="6" t="n">
+        <v>409</v>
+      </c>
+      <c r="F46" s="6" t="n">
+        <v>409</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share-based payment schemes</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n"/>
+      <c r="C47" s="6" t="n"/>
+      <c r="D47" s="6" t="n"/>
+      <c r="E47" s="6" t="n">
+        <v>-442</v>
+      </c>
+      <c r="F47" s="6" t="n">
+        <v>-442</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on ordinary shares</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n"/>
+      <c r="C48" s="6" t="n"/>
+      <c r="D48" s="6" t="n"/>
+      <c r="E48" s="6" t="n">
+        <v>-1348</v>
+      </c>
+      <c r="F48" s="6" t="n">
+        <v>-1348</v>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on preference shares and other shareholders equity</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n"/>
+      <c r="C49" s="6" t="n"/>
+      <c r="D49" s="6" t="n"/>
+      <c r="E49" s="6" t="n">
+        <v>-40</v>
+      </c>
+      <c r="F49" s="6" t="n">
+        <v>-40</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>Net equity impact on inter Barclays PLC Group transfers</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="n"/>
+      <c r="C50" s="6" t="n"/>
+      <c r="D50" s="6" t="n">
+        <v>220</v>
+      </c>
+      <c r="E50" s="6" t="n">
+        <v>-96</v>
+      </c>
+      <c r="F50" s="6" t="n">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E51" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="F51" s="6" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2023</t>
+        </is>
+      </c>
+      <c r="B52" s="5" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C52" s="5" t="n">
+        <v>10765</v>
+      </c>
+      <c r="D52" s="5" t="n">
+        <v>-363</v>
+      </c>
+      <c r="E52" s="5" t="n">
+        <v>47754</v>
+      </c>
+      <c r="F52" s="5" t="n">
+        <v>60504</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n"/>
+      <c r="C53" s="6" t="n">
+        <v>792</v>
+      </c>
+      <c r="D53" s="6" t="n"/>
+      <c r="E53" s="6" t="n">
+        <v>2956</v>
+      </c>
+      <c r="F53" s="6" t="n">
+        <v>3748</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation movements</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n"/>
+      <c r="C54" s="6" t="n"/>
+      <c r="D54" s="6" t="n">
+        <v>-93</v>
+      </c>
+      <c r="E54" s="6" t="n"/>
+      <c r="F54" s="6" t="n">
+        <v>-93</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="n"/>
+      <c r="C55" s="6" t="n"/>
+      <c r="D55" s="6" t="n">
+        <v>-474</v>
+      </c>
+      <c r="E55" s="6" t="n"/>
+      <c r="F55" s="6" t="n">
+        <v>-474</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B56" s="6" t="n"/>
+      <c r="C56" s="6" t="n"/>
+      <c r="D56" s="6" t="n">
+        <v>447</v>
+      </c>
+      <c r="E56" s="6" t="n"/>
+      <c r="F56" s="6" t="n">
+        <v>447</v>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit remeasurement</t>
+        </is>
+      </c>
+      <c r="B57" s="6" t="n"/>
+      <c r="C57" s="6" t="n"/>
+      <c r="D57" s="6" t="n"/>
+      <c r="E57" s="6" t="n">
+        <v>-298</v>
+      </c>
+      <c r="F57" s="6" t="n">
+        <v>-298</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="6" t="inlineStr">
+        <is>
+          <t>Own credit reserve</t>
+        </is>
+      </c>
+      <c r="B58" s="6" t="n"/>
+      <c r="C58" s="6" t="n"/>
+      <c r="D58" s="6" t="n">
+        <v>-822</v>
+      </c>
+      <c r="E58" s="6" t="n"/>
+      <c r="F58" s="6" t="n">
+        <v>-822</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B59" s="5" t="n"/>
+      <c r="C59" s="5" t="n">
+        <v>792</v>
+      </c>
+      <c r="D59" s="5" t="n">
+        <v>-942</v>
+      </c>
+      <c r="E59" s="5" t="n">
+        <v>2658</v>
+      </c>
+      <c r="F59" s="5" t="n">
+        <v>2508</v>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity instruments</t>
+        </is>
+      </c>
+      <c r="B60" s="6" t="n"/>
+      <c r="C60" s="6" t="n">
+        <v>-1161</v>
+      </c>
+      <c r="D60" s="6" t="n"/>
+      <c r="E60" s="6" t="n">
+        <v>-92</v>
+      </c>
+      <c r="F60" s="6" t="n">
+        <v>-1253</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B61" s="6" t="n"/>
+      <c r="C61" s="6" t="n">
+        <v>-792</v>
+      </c>
+      <c r="D61" s="6" t="n"/>
+      <c r="E61" s="6" t="n"/>
+      <c r="F61" s="6" t="n">
+        <v>-792</v>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="6" t="inlineStr">
+        <is>
+          <t>Employee settled Barclays PLC share schemes</t>
+        </is>
+      </c>
+      <c r="B62" s="6" t="n"/>
+      <c r="C62" s="6" t="n"/>
+      <c r="D62" s="6" t="n"/>
+      <c r="E62" s="6" t="n">
+        <v>531</v>
+      </c>
+      <c r="F62" s="6" t="n">
+        <v>531</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share-based payment schemes</t>
+        </is>
+      </c>
+      <c r="B63" s="6" t="n"/>
+      <c r="C63" s="6" t="n"/>
+      <c r="D63" s="6" t="n"/>
+      <c r="E63" s="6" t="n">
+        <v>-448</v>
+      </c>
+      <c r="F63" s="6" t="n">
+        <v>-448</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on ordinary shares</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="n"/>
+      <c r="C64" s="6" t="n"/>
+      <c r="D64" s="6" t="n"/>
+      <c r="E64" s="6" t="n">
+        <v>-1782</v>
+      </c>
+      <c r="F64" s="6" t="n">
+        <v>-1782</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on preference shares and other shareholders equity</t>
+        </is>
+      </c>
+      <c r="B65" s="6" t="n"/>
+      <c r="C65" s="6" t="n"/>
+      <c r="D65" s="6" t="n"/>
+      <c r="E65" s="6" t="n">
+        <v>-41</v>
+      </c>
+      <c r="F65" s="6" t="n">
+        <v>-41</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B66" s="6" t="n"/>
+      <c r="C66" s="6" t="n"/>
+      <c r="D66" s="6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E66" s="6" t="n">
+        <v>-10</v>
+      </c>
+      <c r="F66" s="6" t="n">
+        <v>-7</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2024</t>
+        </is>
+      </c>
+      <c r="B67" s="5" t="n">
+        <v>2348</v>
+      </c>
+      <c r="C67" s="5" t="n">
+        <v>9604</v>
+      </c>
+      <c r="D67" s="5" t="n">
+        <v>-1302</v>
+      </c>
+      <c r="E67" s="5" t="n">
+        <v>48570</v>
+      </c>
+      <c r="F67" s="5" t="n">
+        <v>59220</v>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="6" t="inlineStr">
+        <is>
+          <t>Profit after tax</t>
+        </is>
+      </c>
+      <c r="B68" s="6" t="n"/>
+      <c r="C68" s="6" t="n">
+        <v>783</v>
+      </c>
+      <c r="D68" s="6" t="n"/>
+      <c r="E68" s="6" t="n">
+        <v>3875</v>
+      </c>
+      <c r="F68" s="6" t="n">
+        <v>4658</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="6" t="inlineStr">
+        <is>
+          <t>Currency translation movements</t>
+        </is>
+      </c>
+      <c r="B69" s="6" t="n"/>
+      <c r="C69" s="6" t="n"/>
+      <c r="D69" s="6" t="n">
+        <v>-1156</v>
+      </c>
+      <c r="E69" s="6" t="n"/>
+      <c r="F69" s="6" t="n">
+        <v>-1156</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="6" t="inlineStr">
+        <is>
+          <t>Fair value through other comprehensive income reserve</t>
+        </is>
+      </c>
+      <c r="B70" s="6" t="n"/>
+      <c r="C70" s="6" t="n"/>
+      <c r="D70" s="6" t="n">
+        <v>667</v>
+      </c>
+      <c r="E70" s="6" t="n"/>
+      <c r="F70" s="6" t="n">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="6" t="inlineStr">
+        <is>
+          <t>Cash flow hedges</t>
+        </is>
+      </c>
+      <c r="B71" s="6" t="n"/>
+      <c r="C71" s="6" t="n"/>
+      <c r="D71" s="6" t="n">
+        <v>1541</v>
+      </c>
+      <c r="E71" s="6" t="n"/>
+      <c r="F71" s="6" t="n">
+        <v>1541</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="6" t="inlineStr">
+        <is>
+          <t>Retirement benefit remeasurement</t>
+        </is>
+      </c>
+      <c r="B72" s="6" t="n"/>
+      <c r="C72" s="6" t="n"/>
+      <c r="D72" s="6" t="n"/>
+      <c r="E72" s="6" t="n">
+        <v>-16</v>
+      </c>
+      <c r="F72" s="6" t="n">
+        <v>-16</v>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" s="6" t="inlineStr">
+        <is>
+          <t>Own credit reserve</t>
+        </is>
+      </c>
+      <c r="B73" s="6" t="n"/>
+      <c r="C73" s="6" t="n"/>
+      <c r="D73" s="6" t="n">
+        <v>63</v>
+      </c>
+      <c r="E73" s="6" t="n"/>
+      <c r="F73" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" s="5" t="inlineStr">
+        <is>
+          <t>Total comprehensive income for the year</t>
+        </is>
+      </c>
+      <c r="B74" s="5" t="n"/>
+      <c r="C74" s="5" t="n">
+        <v>783</v>
+      </c>
+      <c r="D74" s="5" t="n">
+        <v>1115</v>
+      </c>
+      <c r="E74" s="5" t="n">
+        <v>3859</v>
+      </c>
+      <c r="F74" s="5" t="n">
+        <v>5757</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" s="6" t="inlineStr">
+        <is>
+          <t>Issue and redemption of other equity instruments</t>
+        </is>
+      </c>
+      <c r="B75" s="6" t="n"/>
+      <c r="C75" s="6" t="n">
+        <v>842</v>
+      </c>
+      <c r="D75" s="6" t="n"/>
+      <c r="E75" s="6" t="n">
+        <v>-5</v>
+      </c>
+      <c r="F75" s="6" t="n">
+        <v>837</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" s="6" t="inlineStr">
+        <is>
+          <t>Other equity instruments coupons paid</t>
+        </is>
+      </c>
+      <c r="B76" s="6" t="n"/>
+      <c r="C76" s="6" t="n">
+        <v>-783</v>
+      </c>
+      <c r="D76" s="6" t="n"/>
+      <c r="E76" s="6" t="n"/>
+      <c r="F76" s="6" t="n">
+        <v>-783</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" s="6" t="inlineStr">
+        <is>
+          <t>Redemption of preference shares</t>
+        </is>
+      </c>
+      <c r="B77" s="6" t="n">
+        <v>-2</v>
+      </c>
+      <c r="C77" s="6" t="n"/>
+      <c r="D77" s="6" t="n">
+        <v>2</v>
+      </c>
+      <c r="E77" s="6" t="n">
+        <v>-270</v>
+      </c>
+      <c r="F77" s="6" t="n">
+        <v>-270</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" s="6" t="inlineStr">
+        <is>
+          <t>Employee settled Barclays PLC share schemes</t>
+        </is>
+      </c>
+      <c r="B78" s="6" t="n"/>
+      <c r="C78" s="6" t="n"/>
+      <c r="D78" s="6" t="n"/>
+      <c r="E78" s="6" t="n">
+        <v>667</v>
+      </c>
+      <c r="F78" s="6" t="n">
+        <v>667</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" s="6" t="inlineStr">
+        <is>
+          <t>Vesting of Barclays PLC shares under share-based payment schemes</t>
+        </is>
+      </c>
+      <c r="B79" s="6" t="n"/>
+      <c r="C79" s="6" t="n"/>
+      <c r="D79" s="6" t="n"/>
+      <c r="E79" s="6" t="n">
+        <v>-530</v>
+      </c>
+      <c r="F79" s="6" t="n">
+        <v>-530</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on ordinary shares</t>
+        </is>
+      </c>
+      <c r="B80" s="6" t="n"/>
+      <c r="C80" s="6" t="n"/>
+      <c r="D80" s="6" t="n"/>
+      <c r="E80" s="6" t="n">
+        <v>-2570</v>
+      </c>
+      <c r="F80" s="6" t="n">
+        <v>-2570</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" s="6" t="inlineStr">
+        <is>
+          <t>Dividends on preference shares and other shareholders equity</t>
+        </is>
+      </c>
+      <c r="B81" s="6" t="n"/>
+      <c r="C81" s="6" t="n"/>
+      <c r="D81" s="6" t="n"/>
+      <c r="E81" s="6" t="n">
+        <v>-32</v>
+      </c>
+      <c r="F81" s="6" t="n">
+        <v>-32</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" s="6" t="inlineStr">
+        <is>
+          <t>Other reserve movements</t>
+        </is>
+      </c>
+      <c r="B82" s="6" t="n"/>
+      <c r="C82" s="6" t="n"/>
+      <c r="D82" s="6" t="n">
+        <v>6</v>
+      </c>
+      <c r="E82" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="F82" s="6" t="n">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" s="5" t="inlineStr">
+        <is>
+          <t>Balance as at 31 December 2025</t>
+        </is>
+      </c>
+      <c r="B83" s="5" t="n">
+        <v>2346</v>
+      </c>
+      <c r="C83" s="5" t="n">
+        <v>10446</v>
+      </c>
+      <c r="D83" s="5" t="n">
+        <v>-179</v>
+      </c>
+      <c r="E83" s="5" t="n">
+        <v>49700</v>
+      </c>
+      <c r="F83" s="5" t="n">
+        <v>62313</v>
+      </c>
+    </row>
+    <row r="85" ht="220" customHeight="1">
+      <c r="A85" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC consolidated financial statements ("Barclays Bank Group"), £m, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.284-289 (Consolidated income statement / statement of comprehensive income / balance sheet / statement of changes in equity) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 balance sheet &amp; equity comparative: Barclays Bank PLC Annual Report 2024, p.268-271 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021 (restated): Barclays Bank PLC Annual Report 2022, p.166-170 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
+Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) was not sourced within this batch's reviewed pages of the FY2022 Annual Report - only that year's Profit after tax and Total comprehensive income (from the Statement of Changes in Equity) are populated; the underlying OCI note itself was not reviewed.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A85:F85"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -3410,16 +8724,16 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="62" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3430,445 +8744,449 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — CET1 Capital</t>
+          <t>Barclays Bank PLC — Asset Quality</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Barclays Bank PLC Group (consolidated basis), £m. See source note at bottom.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£m)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£m)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£m)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£m)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£m)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>28177</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>26995</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>25470</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>25907</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>23928</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Loans and advances at amortised cost, by IFRS 9 stage (gross exposure)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>238476</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>215878</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>233240</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>211001</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>186418</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>7751</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>8128</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>8430</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>14194</v>
+      </c>
+      <c r="F6" s="6" t="n">
+        <v>12820</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>2220</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1795</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1822</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>1802</v>
+      </c>
+      <c r="F7" s="6" t="n">
+        <v>1731</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="5" t="inlineStr">
+        <is>
+          <t>Total gross exposure</t>
+        </is>
+      </c>
+      <c r="B8" s="5" t="n">
+        <v>248447</v>
+      </c>
+      <c r="C8" s="5" t="n">
+        <v>225801</v>
+      </c>
+      <c r="D8" s="5" t="n">
+        <v>243492</v>
+      </c>
+      <c r="E8" s="5" t="n">
+        <v>226997</v>
+      </c>
+      <c r="F8" s="5" t="n">
+        <v>200969</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="5" t="inlineStr">
+        <is>
+          <t>Allowance for expected credit losses, by IFRS 9 stage</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n"/>
+      <c r="C9" s="6" t="n"/>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Stage 1</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>133</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>140</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>178</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>321</v>
+      </c>
+      <c r="F10" s="6" t="n">
+        <v>221</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="6" t="inlineStr">
+        <is>
+          <t>Stage 2</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n">
+        <v>191</v>
+      </c>
+      <c r="C11" s="6" t="n">
+        <v>219</v>
+      </c>
+      <c r="D11" s="6" t="n">
+        <v>265</v>
+      </c>
+      <c r="E11" s="6" t="n">
+        <v>276</v>
+      </c>
+      <c r="F11" s="6" t="n">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>571</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>390</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>610</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>617</v>
+      </c>
+      <c r="F12" s="6" t="n">
+        <v>769</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="5" t="inlineStr">
+        <is>
+          <t>Total allowance for expected credit losses</t>
+        </is>
+      </c>
+      <c r="B13" s="5" t="n">
+        <v>895</v>
+      </c>
+      <c r="C13" s="5" t="n">
+        <v>749</v>
+      </c>
+      <c r="D13" s="5" t="n">
+        <v>1053</v>
+      </c>
+      <c r="E13" s="5" t="n">
+        <v>1214</v>
+      </c>
+      <c r="F13" s="5" t="n">
+        <v>1187</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Net exposure</t>
+        </is>
+      </c>
+      <c r="B14" s="5" t="n">
+        <v>247552</v>
+      </c>
+      <c r="C14" s="5" t="n">
+        <v>225052</v>
+      </c>
+      <c r="D14" s="5" t="n">
+        <v>242439</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>225783</v>
+      </c>
+      <c r="F14" s="5" t="n">
+        <v>199782</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="5" t="inlineStr">
+        <is>
+          <t>Of which: Corporate loans (FY2023-25) / Wholesale loans (FY2021-22)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Gross exposure</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n">
+        <v>240970</v>
+      </c>
+      <c r="C16" s="6" t="n">
+        <v>218371</v>
+      </c>
+      <c r="D16" s="6" t="n">
+        <v>236273</v>
+      </c>
+      <c r="E16" s="6" t="n">
+        <v>215265</v>
+      </c>
+      <c r="F16" s="6" t="n">
+        <v>189648</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Allowance for expected credit losses</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n">
+        <v>854</v>
+      </c>
+      <c r="C17" s="6" t="n">
+        <v>700</v>
+      </c>
+      <c r="D17" s="6" t="n">
+        <v>729</v>
+      </c>
+      <c r="E17" s="6" t="n">
+        <v>739</v>
+      </c>
+      <c r="F17" s="6" t="n">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="5" t="inlineStr">
+        <is>
+          <t>Asset quality ratios</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>ECL coverage (Total allowance / Total gross exposure)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>0.5%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="inlineStr">
+        <is>
+          <t>0.6%</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 / NPL ratio (Stage 3 gross / Total gross)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>Stage 3 coverage (Stage 3 allowance / Stage 3 gross)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="inlineStr">
+        <is>
+          <t>25.7%</t>
+        </is>
+      </c>
+      <c r="C21" s="6" t="inlineStr">
+        <is>
+          <t>21.7%</t>
+        </is>
+      </c>
+      <c r="D21" s="6" t="inlineStr">
+        <is>
+          <t>33.5%</t>
+        </is>
+      </c>
+      <c r="E21" s="6" t="inlineStr">
+        <is>
+          <t>34.2%</t>
+        </is>
+      </c>
+      <c r="F21" s="6" t="inlineStr">
+        <is>
+          <t>44.4%</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="220" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>ASSET QUALITY NOTE - IFRS 9 stage breakdown from the 'Credit risk' section of the Risk review (Loans and advances at amortised cost, audited), each Annual Report's own tables, closing (31 December) balances only:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.175-176 (FY2025 stage rollforward) and p.180 (FY2024 comparative) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023 (&amp; FY2022 comparative used for the FY2023 rollforward's opening balance): Barclays Bank PLC Annual Report 2024, p.175 (Loans and advances at amortised cost stage rollforward, Retail mortgages / Retail other / Corporate loans by-product breakdown, summed to a Total across products here) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.76 (Gross exposure / Impairment allowance / Net exposure / Coverage ratio by stage, Home loans / Credit cards, unsecured loans and other retail lending / Wholesale loans by-product breakdown, summed to a Total across products here) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
+PRESENTATION NOTE: FY2021-22's own tables use a 3-way product split (Home loans / Credit cards, unsecured loans and other retail lending / Wholesale loans) that differs from FY2023-25's split (Retail mortgages / Retail other / Corporate loans) - a genuine, disclosed business change, not a reclassification of the same book: the FY2024 Annual Report states 'Barclays Bank PLC does not have retail credit card lending', i.e. the credit card book present in the FY2021-22 'Credit cards, unsecured loans...' line was moved out of this entity's retail scope by FY2023. Each year's own total is reproduced as its own source states it, not forced onto a common product taxonomy; the 'Of which' subtotal row is labelled 'Corporate loans (FY2023-25) / Wholesale loans (FY2021-22)' to flag this is the closest analogous category, not a like-for-like match. Note the Credit risk section's own 'Loans and advances at amortised cost' gross exposure total (£248,447m FY2025) is materially larger than the Balance Sheet's 'Loans and advances at amortised cost to customers' line (£141,750m FY2025) - the Credit risk section evidently uses a broader internal credit-exposure definition (e.g. including reverse repos/cash collateral classified elsewhere on the Balance Sheet) than the statutory Balance Sheet caption; both are reproduced as their own source discloses them, not reconciled.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank PLC — CET1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo-consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>12.9%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank PLC — Tier 1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo-consolidated basis, £m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 (T1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>35848</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>33787</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>33864</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>34139</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>32395</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank PLC — Tier 1 Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo-consolidated basis, % of RWA</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Tier 1 (T1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A23:F23"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -3894,7 +9212,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total Capital</t>
+          <t>Barclays Bank PLC — CET1 Capital</t>
         </is>
       </c>
     </row>
@@ -3940,23 +9258,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
+          <t>Common Equity Tier 1 (CET1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>42129</v>
+        <v>28177</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>40444</v>
+        <v>26995</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>40530</v>
+        <v>25470</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>42321</v>
+        <v>25907</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>37954</v>
+        <v>23928</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -4005,7 +9323,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total Capital Ratio</t>
+          <t>Barclays Bank PLC — CET1 Ratio</t>
         </is>
       </c>
     </row>
@@ -4051,32 +9369,32 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital ratio</t>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
         </is>
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>19.0%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>18.1%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>19.2%</t>
+          <t>12.1%</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>20.8%</t>
+          <t>12.7%</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>20.5%</t>
+          <t>12.9%</t>
         </is>
       </c>
     </row>
@@ -4126,7 +9444,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total RWAs</t>
+          <t>Barclays Bank PLC — Tier 1 Capital</t>
         </is>
       </c>
     </row>
@@ -4172,29 +9490,29 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk weighted assets (RWAs)</t>
+          <t>Tier 1 (T1) capital</t>
         </is>
       </c>
       <c r="B4" s="6" t="n">
-        <v>222247</v>
+        <v>35848</v>
       </c>
       <c r="C4" s="6" t="n">
-        <v>223648</v>
+        <v>33787</v>
       </c>
       <c r="D4" s="6" t="n">
-        <v>211193</v>
+        <v>33864</v>
       </c>
       <c r="E4" s="6" t="n">
-        <v>203833</v>
+        <v>34139</v>
       </c>
       <c r="F4" s="6" t="n">
-        <v>185467</v>
+        <v>32395</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -3092,7 +3092,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -3203,7 +3203,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -3324,7 +3324,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -3435,7 +3435,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -3711,7 +3711,7 @@
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -3854,7 +3854,7 @@
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -3947,7 +3947,9 @@
       <c r="D4" s="6" t="n">
         <v>339</v>
       </c>
-      <c r="E4" s="6" t="n"/>
+      <c r="E4" s="6" t="n">
+        <v>310</v>
+      </c>
       <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
@@ -3965,7 +3967,9 @@
       <c r="D5" s="6" t="n">
         <v>308</v>
       </c>
-      <c r="E5" s="6" t="n"/>
+      <c r="E5" s="6" t="n">
+        <v>288</v>
+      </c>
       <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
@@ -4003,7 +4007,7 @@
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR is an average of the last four spot quarter-end ratios. It was not a UK regulatory requirement as at FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2021 figure is available. Available/Required Stable Funding £bn breakdown was not located for FY2022 within the reviewed pages (only the ratio, 108%, was disclosed there); the ratio alone is reported for that year.</t>
+          <t>Note: NSFR is an average of the last four spot quarter-end ratios. It was not a UK regulatory requirement as at FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2021 figure is available.</t>
         </is>
       </c>
     </row>
@@ -4011,7 +4015,7 @@
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -4128,7 +4132,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -5155,7 +5159,7 @@
 FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.284-289 (Consolidated income statement / statement of comprehensive income / balance sheet / statement of changes in equity) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023 balance sheet &amp; equity comparative: Barclays Bank PLC Annual Report 2024, p.268-271 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021 (restated): Barclays Bank PLC Annual Report 2022, p.166-170 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
-Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) was not sourced within this batch's reviewed pages of the FY2022 Annual Report - only that year's Profit after tax and Total comprehensive income (from the Statement of Changes in Equity) are populated; the underlying OCI note itself was not reviewed.</t>
+Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) is sourced from the same FY2022 Annual Report's restated 2021 comparative column in its Consolidated statement of comprehensive income (p.166); this cross-checks exactly against the FY2021 movements in the Statement of Changes in Equity.</t>
         </is>
       </c>
     </row>
@@ -5786,7 +5790,9 @@
       <c r="E30" s="6" t="n">
         <v>2411</v>
       </c>
-      <c r="F30" s="6" t="n"/>
+      <c r="F30" s="6" t="n">
+        <v>-155</v>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -5806,7 +5812,9 @@
       <c r="E31" s="6" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="6" t="n"/>
+      <c r="F31" s="6" t="n">
+        <v>0</v>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="6" t="inlineStr">
@@ -5826,7 +5834,9 @@
       <c r="E32" s="6" t="n">
         <v>-6376</v>
       </c>
-      <c r="F32" s="6" t="n"/>
+      <c r="F32" s="6" t="n">
+        <v>-1383</v>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -5846,7 +5856,9 @@
       <c r="E33" s="6" t="n">
         <v>68</v>
       </c>
-      <c r="F33" s="6" t="n"/>
+      <c r="F33" s="6" t="n">
+        <v>-248</v>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -5866,7 +5878,9 @@
       <c r="E34" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="F34" s="6" t="n"/>
+      <c r="F34" s="6" t="n">
+        <v>-6</v>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -5886,7 +5900,9 @@
       <c r="E35" s="6" t="n">
         <v>4627</v>
       </c>
-      <c r="F35" s="6" t="n"/>
+      <c r="F35" s="6" t="n">
+        <v>1105</v>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -5906,7 +5922,9 @@
       <c r="E36" s="6" t="n">
         <v>449</v>
       </c>
-      <c r="F36" s="6" t="n"/>
+      <c r="F36" s="6" t="n">
+        <v>170</v>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -5926,7 +5944,9 @@
       <c r="E37" s="6" t="n">
         <v>-7290</v>
       </c>
-      <c r="F37" s="6" t="n"/>
+      <c r="F37" s="6" t="n">
+        <v>-2212</v>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -5946,7 +5966,9 @@
       <c r="E38" s="6" t="n">
         <v>543</v>
       </c>
-      <c r="F38" s="6" t="n"/>
+      <c r="F38" s="6" t="n">
+        <v>-327</v>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -5966,7 +5988,9 @@
       <c r="E39" s="6" t="n">
         <v>1808</v>
       </c>
-      <c r="F39" s="6" t="n"/>
+      <c r="F39" s="6" t="n">
+        <v>740</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -5986,7 +6010,9 @@
       <c r="E40" s="5" t="n">
         <v>-3752</v>
       </c>
-      <c r="F40" s="5" t="n"/>
+      <c r="F40" s="5" t="n">
+        <v>-2316</v>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -6006,7 +6032,9 @@
       <c r="E41" s="6" t="n">
         <v>-755</v>
       </c>
-      <c r="F41" s="6" t="n"/>
+      <c r="F41" s="6" t="n">
+        <v>1299</v>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -6026,7 +6054,9 @@
       <c r="E42" s="6" t="n">
         <v>2092</v>
       </c>
-      <c r="F42" s="6" t="n"/>
+      <c r="F42" s="6" t="n">
+        <v>-105</v>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -6046,7 +6076,9 @@
       <c r="E43" s="6" t="n">
         <v>-156</v>
       </c>
-      <c r="F43" s="6" t="n"/>
+      <c r="F43" s="6" t="n">
+        <v>-563</v>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
@@ -6066,7 +6098,9 @@
       <c r="E44" s="5" t="n">
         <v>1181</v>
       </c>
-      <c r="F44" s="5" t="n"/>
+      <c r="F44" s="5" t="n">
+        <v>631</v>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -6086,7 +6120,9 @@
       <c r="E45" s="5" t="n">
         <v>-2571</v>
       </c>
-      <c r="F45" s="5" t="n"/>
+      <c r="F45" s="5" t="n">
+        <v>-1685</v>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
@@ -6117,7 +6153,7 @@
 FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.284-289 (Consolidated income statement / statement of comprehensive income / balance sheet / statement of changes in equity) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023 balance sheet &amp; equity comparative: Barclays Bank PLC Annual Report 2024, p.268-271 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021 (restated): Barclays Bank PLC Annual Report 2022, p.166-170 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
-Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) was not sourced within this batch's reviewed pages of the FY2022 Annual Report - only that year's Profit after tax and Total comprehensive income (from the Statement of Changes in Equity) are populated; the underlying OCI note itself was not reviewed.</t>
+Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) is sourced from the same FY2022 Annual Report's restated 2021 comparative column in its Consolidated statement of comprehensive income (p.166); this cross-checks exactly against the FY2021 movements in the Statement of Changes in Equity.</t>
         </is>
       </c>
     </row>
@@ -7571,7 +7607,7 @@
 FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.284-289 (Consolidated income statement / statement of comprehensive income / balance sheet / statement of changes in equity) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023 balance sheet &amp; equity comparative: Barclays Bank PLC Annual Report 2024, p.268-271 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021 (restated): Barclays Bank PLC Annual Report 2022, p.166-170 — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0
-Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) was not sourced within this batch's reviewed pages of the FY2022 Annual Report - only that year's Profit after tax and Total comprehensive income (from the Statement of Changes in Equity) are populated; the underlying OCI note itself was not reviewed.</t>
+Note: FY2021 figures are restated (2022 Over-issuance of Securities matter in the US; see Note 1a in the FY2022 Annual Report), consistent with the Cash Flow Statement and Pillar 3 sheets in this workbook. 'UK regulatory levies' was not a separate income statement line until FY2023 - blank for FY2022/FY2021 rather than folded into another line. FY2021's other comprehensive income detail (currency translation, FVOCI, cash flow hedge, retirement benefit, own credit rows) is sourced from the same FY2022 Annual Report's restated 2021 comparative column in its Consolidated statement of comprehensive income (p.166); this cross-checks exactly against the FY2021 movements in the Statement of Changes in Equity.</t>
         </is>
       </c>
     </row>
@@ -9288,7 +9324,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -9409,7 +9445,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>
@@ -9520,7 +9556,7 @@
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.231-233 (Capital risk / Liquidity risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
 FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
 FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
         </is>

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -3456,10 +3456,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F6"/>
+  <dimension ref="A1:F21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="54" customWidth="1" min="1" max="1"/>
+    <col width="58" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -3477,7 +3477,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis</t>
+          <t>Solo-consolidated basis, £m. FY2025-FY2022 per the UK OV1 template; FY2021 per a differently-categorised table - see source note at bottom.</t>
         </is>
       </c>
     </row>
@@ -3489,73 +3489,308 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>FY2025</t>
+          <t>FY2025 (£m)</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
         <is>
-          <t>FY2024</t>
+          <t>FY2024 (£m)</t>
         </is>
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>FY2023</t>
+          <t>FY2023 (£m)</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
         <is>
-          <t>FY2022</t>
+          <t>FY2022 (£m)</t>
         </is>
       </c>
       <c r="F3" s="4" t="inlineStr">
         <is>
-          <t>FY2021</t>
+          <t>FY2021 (£m)</t>
         </is>
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>RWA category breakdown</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not publicly disclosed</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="150" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC's own 'Capital risk' section of the Risk review (see p3_sources() URLs above):
-NOT PUBLICLY DISCLOSED within the Annual Report: the Capital risk section (p.231 of the FY2025 Annual Report) discloses only the single aggregate Total RWAs figure and capital ratios, not a UK OV1-style breakdown by credit/counterparty credit/market/operational risk - confirmed by reading that section in full. The Annual Report itself references a separate, standalone 'Barclays Bank PLC 2025 Pillar 3 Report' as the source for further risk-profile detail, but that document was not sourced within this batch's reviewed pages.</t>
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>UK OV1 — Overview of risk weighted exposure amounts (solo-consolidated)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (excluding CCR)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
+        <v>109036</v>
+      </c>
+      <c r="C5" s="6" t="n">
+        <v>106697</v>
+      </c>
+      <c r="D5" s="6" t="n">
+        <v>99934</v>
+      </c>
+      <c r="E5" s="6" t="n">
+        <v>105321</v>
+      </c>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (CCR, incl. CVA)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n">
+        <v>41109</v>
+      </c>
+      <c r="C6" s="6" t="n">
+        <v>45839</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>37163</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>33746</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Settlement risk</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>153</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>115</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>67</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>53</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Securitisation exposures in the non-trading book</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>23512</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>20407</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>16159</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>15043</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (position, FX and commodities)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>25534</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>28172</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>37010</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>29642</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n">
+        <v>22903</v>
+      </c>
+      <c r="C10" s="6" t="n">
+        <v>22418</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>20860</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>20028</v>
+      </c>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Total risk weighted exposure amount</t>
+        </is>
+      </c>
+      <c r="B11" s="5" t="n">
+        <v>222247</v>
+      </c>
+      <c r="C11" s="5" t="n">
+        <v>223648</v>
+      </c>
+      <c r="D11" s="5" t="n">
+        <v>211193</v>
+      </c>
+      <c r="E11" s="5" t="n">
+        <v>203833</v>
+      </c>
+      <c r="F11" s="5" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="5" t="inlineStr">
+        <is>
+          <t>Table 5: RWAs by risk type (Barclays Bank PLC's own table, solo-consolidated - different categorisation to the UK OV1 rows above, see sources note)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n"/>
+      <c r="C12" s="6" t="n"/>
+      <c r="D12" s="6" t="n"/>
+      <c r="E12" s="6" t="n"/>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>Credit risk (Standardised + AIRB approaches)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n"/>
+      <c r="D13" s="6" t="n"/>
+      <c r="E13" s="6" t="n"/>
+      <c r="F13" s="6" t="n">
+        <v>100280</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="6" t="inlineStr">
+        <is>
+          <t>Counterparty credit risk (Standardised + AIRB approaches)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n">
+        <v>31251</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>Credit valuation adjustment (CVA)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="n"/>
+      <c r="C15" s="6" t="n"/>
+      <c r="D15" s="6" t="n"/>
+      <c r="E15" s="6" t="n"/>
+      <c r="F15" s="6" t="n">
+        <v>1862</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>Settlement risk</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="n"/>
+      <c r="D16" s="6" t="n"/>
+      <c r="E16" s="6" t="n"/>
+      <c r="F16" s="6" t="n">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>Market risk (Standardised + IMA approaches)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="n"/>
+      <c r="C17" s="6" t="n"/>
+      <c r="D17" s="6" t="n"/>
+      <c r="E17" s="6" t="n"/>
+      <c r="F17" s="6" t="n">
+        <v>34827</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>Operational risk</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="n"/>
+      <c r="D18" s="6" t="n"/>
+      <c r="E18" s="6" t="n"/>
+      <c r="F18" s="6" t="n">
+        <v>17184</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>Total RWAs</t>
+        </is>
+      </c>
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+      <c r="D19" s="5" t="n"/>
+      <c r="E19" s="5" t="n"/>
+      <c r="F19" s="5" t="n">
+        <v>185467</v>
+      </c>
+    </row>
+    <row r="21" ht="240" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC's own dedicated Pillar 3 Reports (solo-consolidated basis, matching the Total RWAs sheet's own basis and figures every year below - confirmed by cross-checking each year's Total row against the Total RWAs sheet), not the Annual Report's Capital risk section (which discloses only the aggregate Total RWAs figure and capital ratios, no category breakdown):
+FY2025 &amp; FY2024 (DIRECTLY DISCLOSED): Barclays Bank PLC Pillar 3 Report 2025, Table 5 'UK OV1 - Overview of risk weighted exposure amounts', p.11 (FY2025 own-year column and FY2024 comparative column, both £m) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBPLC-Pillar-3.pdf
+FY2023 (DIRECTLY DISCLOSED, cross-checked against the FY2024 own-year Pillar 3 Report below): Barclays Bank PLC Pillar 3 Report 2024, Table 6 'UK OV1 - Overview of risk weighted exposure amounts', p.12 (31.12.2023 comparative column) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2024Results/FY24-Barclays-Bank-PLC-Pillar-3-Report.pdf
+FY2022 (DIRECTLY DISCLOSED): Barclays Bank PLC Pillar 3 Report 2022, Table 6 'UK OV1 - Overview of risk weighted exposure amounts', p.11 (31.12.2022 column) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2022/Pillar-3/Barclays-Bank-PLC-Pillar-3-Report%202022.pdf
+All four years reconcile exactly to their own Total row and to the Total RWAs sheet's own figure for that year (£222,247m / £223,648m / £211,193m / £203,833m respectively). Each report's own UK OV1 table additionally discloses a 'credit valuation adjustment (CVA)' sub-line (row UK8b: £2,150m/£1,938m/£2,510m/£2,465m for FY2025-FY2022 respectively) nested inside, and already included within, the Counterparty credit risk (CCR) row shown below - not broken out as its own row here, and not separately additive to the Total.
+FY2021 (DIRECTLY DISCLOSED, but a DIFFERENT table/categorisation - Barclays Bank PLC's dedicated Pillar 3 Report does not exist as a standalone document for FY2021, so this year is instead sourced from the FY2021 comparative column of the FY2022 Pillar 3 Report's own separate 'Table 5: RWAs by risk type' - not that report's UK OV1 table, which only carries a current-year/Q3 comparative, not FY2021): Barclays Bank PLC Pillar 3 Report 2022, Table 5 'RWAs by risk type', p.10 ('As at 31 December 2021' row) — https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2022/Pillar-3/Barclays-Bank-PLC-Pillar-3-Report%202022.pdf
+This table splits Credit risk / Counterparty credit risk (CCR) / Market risk each into their Standardised and internal-model-approach sub-columns (summed here into one Credit risk / CCR / Market risk row apiece) and, unlike the UK OV1 template, shows Credit valuation adjustment (CVA) as its own separate row rather than a sub-line nested inside CCR, and carries no separate Securitisation exposures row at all - so FY2021's row boundaries are NOT directly comparable line-for-line to the UK OV1 rows used for FY2022-FY2025 above (e.g. FY2021's 'Credit risk' may include exposures the OV1 years would classify as Securitisation); every FY2021 category is shown exactly as this table discloses it, in its own labelled section below, and its Total row reconciles exactly to the Total RWAs sheet's own FY2021 figure (£185,467m).</t>
         </is>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A6:F6"/>
+    <mergeCell ref="A21:F21"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -13,18 +13,19 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3006,14 +3007,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Tier 1 Ratio</t>
+          <t>Barclays Bank PLC — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, % of RWA</t>
+          <t>Solo-consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3052,33 +3053,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 (T1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
+          <t>Tier 1 (T1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>35848</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>33787</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>33864</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>34139</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>32395</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3127,14 +3118,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total Capital</t>
+          <t>Barclays Bank PLC — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Solo-consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3173,23 +3164,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>42129</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>40444</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>40530</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>42321</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>37954</v>
+          <t>Tier 1 (T1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3238,14 +3239,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total Capital Ratio</t>
+          <t>Barclays Bank PLC — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, % of RWA</t>
+          <t>Solo-consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3284,33 +3285,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>20.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>42129</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>40444</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>40530</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>42321</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>37954</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -3359,14 +3350,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total RWAs</t>
+          <t>Barclays Bank PLC — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Solo-consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3405,29 +3396,39 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk weighted assets (RWAs)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>222247</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>223648</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>211193</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>203833</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>185467</v>
+          <t>Total regulatory capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
@@ -3451,6 +3452,117 @@
 </file>
 
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk weighted assets (RWAs)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>222247</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>223648</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>211193</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>203833</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>185467</v>
+      </c>
+    </row>
+    <row r="5" ht="60" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="100" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3796,7 +3908,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3961,7 +4073,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4104,7 +4216,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4265,7 +4377,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -9469,10 +9581,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F7"/>
+  <dimension ref="A1:F57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="96" customWidth="1" min="1" max="1"/>
     <col width="15" customWidth="1" min="2" max="2"/>
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
@@ -9483,21 +9595,21 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — CET1 Capital</t>
+          <t>Barclays Bank PLC - KM1 Key Metrics</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Each year from its own Pillar 3 edition's year-end column - both published leverage bases shown</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="4" t="inlineStr">
         <is>
-          <t>Metric</t>
+          <t>Line item</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
@@ -9527,48 +9639,1143 @@
       </c>
     </row>
     <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>Available own funds (amounts)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n"/>
+      <c r="C4" s="6" t="n"/>
+      <c r="D4" s="6" t="n"/>
+      <c r="E4" s="6" t="n"/>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>1  Common Equity Tier 1 (CET1) capital (£m)</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="n">
         <v>28177</v>
       </c>
-      <c r="C4" s="6" t="n">
+      <c r="C5" s="6" t="n">
         <v>26995</v>
       </c>
-      <c r="D4" s="6" t="n">
+      <c r="D5" s="6" t="n">
         <v>25470</v>
       </c>
-      <c r="E4" s="6" t="n">
+      <c r="E5" s="6" t="n">
         <v>25907</v>
       </c>
-      <c r="F4" s="6" t="n">
-        <v>23928</v>
-      </c>
-    </row>
-    <row r="5" ht="60" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="100" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+      <c r="F5" s="6" t="n"/>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>1a  Fully loaded common Equity Tier 1 (CET1) capital (£m)</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="n"/>
+      <c r="C6" s="6" t="n">
+        <v>26992</v>
+      </c>
+      <c r="D6" s="6" t="n">
+        <v>25450</v>
+      </c>
+      <c r="E6" s="6" t="n">
+        <v>25571</v>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>2  Tier 1 capital (£m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>35848</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>33787</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>33864</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>34139</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>2a  Fully loaded tier 1 capital (£m)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n"/>
+      <c r="C8" s="6" t="n">
+        <v>33783</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>33844</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>33802</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>3  Total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="n">
+        <v>42129</v>
+      </c>
+      <c r="C9" s="6" t="n">
+        <v>40444</v>
+      </c>
+      <c r="D9" s="6" t="n">
+        <v>40530</v>
+      </c>
+      <c r="E9" s="6" t="n">
+        <v>42321</v>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10">
+      <c r="A10" s="6" t="inlineStr">
+        <is>
+          <t>3a  Fully loaded total capital (£m)</t>
+        </is>
+      </c>
+      <c r="B10" s="6" t="n"/>
+      <c r="C10" s="6" t="n">
+        <v>39912</v>
+      </c>
+      <c r="D10" s="6" t="n">
+        <v>39981</v>
+      </c>
+      <c r="E10" s="6" t="n">
+        <v>41092</v>
+      </c>
+      <c r="F10" s="6" t="n"/>
+    </row>
+    <row r="11">
+      <c r="A11" s="5" t="inlineStr">
+        <is>
+          <t>Risk-weighted exposure amounts</t>
+        </is>
+      </c>
+      <c r="B11" s="6" t="n"/>
+      <c r="C11" s="6" t="n"/>
+      <c r="D11" s="6" t="n"/>
+      <c r="E11" s="6" t="n"/>
+      <c r="F11" s="6" t="n"/>
+    </row>
+    <row r="12">
+      <c r="A12" s="6" t="inlineStr">
+        <is>
+          <t>4  Total risk-weighted exposure amount (£m)</t>
+        </is>
+      </c>
+      <c r="B12" s="6" t="n">
+        <v>222247</v>
+      </c>
+      <c r="C12" s="6" t="n">
+        <v>223648</v>
+      </c>
+      <c r="D12" s="6" t="n">
+        <v>211193</v>
+      </c>
+      <c r="E12" s="6" t="n">
+        <v>203833</v>
+      </c>
+      <c r="F12" s="6" t="n"/>
+    </row>
+    <row r="13">
+      <c r="A13" s="6" t="inlineStr">
+        <is>
+          <t>4a  Fully loaded total risk-weighted exposure amount (£m)</t>
+        </is>
+      </c>
+      <c r="B13" s="6" t="n"/>
+      <c r="C13" s="6" t="n">
+        <v>223644</v>
+      </c>
+      <c r="D13" s="6" t="n">
+        <v>211173</v>
+      </c>
+      <c r="E13" s="6" t="n">
+        <v>203531</v>
+      </c>
+      <c r="F13" s="6" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="5" t="inlineStr">
+        <is>
+          <t>Capital ratios (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B14" s="6" t="n"/>
+      <c r="C14" s="6" t="n"/>
+      <c r="D14" s="6" t="n"/>
+      <c r="E14" s="6" t="n"/>
+      <c r="F14" s="6" t="n"/>
+    </row>
+    <row r="15">
+      <c r="A15" s="6" t="inlineStr">
+        <is>
+          <t>5  Common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B15" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="C15" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="D15" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="E15" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="F15" s="6" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="6" t="inlineStr">
+        <is>
+          <t>5a  Fully loaded common Equity Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B16" s="6" t="n"/>
+      <c r="C16" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="D16" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="E16" s="6" t="inlineStr">
+        <is>
+          <t>12.6%</t>
+        </is>
+      </c>
+      <c r="F16" s="6" t="n"/>
+    </row>
+    <row r="17">
+      <c r="A17" s="6" t="inlineStr">
+        <is>
+          <t>6  Tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B17" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="C17" s="6" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
+      </c>
+      <c r="D17" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="E17" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F17" s="6" t="n"/>
+    </row>
+    <row r="18">
+      <c r="A18" s="6" t="inlineStr">
+        <is>
+          <t>6a  Fully loaded tier 1 ratio (%)</t>
+        </is>
+      </c>
+      <c r="B18" s="6" t="n"/>
+      <c r="C18" s="6" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
+      </c>
+      <c r="D18" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="E18" s="6" t="inlineStr">
+        <is>
+          <t>16.6%</t>
+        </is>
+      </c>
+      <c r="F18" s="6" t="n"/>
+    </row>
+    <row r="19">
+      <c r="A19" s="6" t="inlineStr">
+        <is>
+          <t>7  Total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B19" s="6" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="C19" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D19" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="E19" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="F19" s="6" t="n"/>
+    </row>
+    <row r="20">
+      <c r="A20" s="6" t="inlineStr">
+        <is>
+          <t>7a  Fully loaded total capital ratio (%)</t>
+        </is>
+      </c>
+      <c r="B20" s="6" t="n"/>
+      <c r="C20" s="6" t="inlineStr">
+        <is>
+          <t>17.8%</t>
+        </is>
+      </c>
+      <c r="D20" s="6" t="inlineStr">
+        <is>
+          <t>18.9%</t>
+        </is>
+      </c>
+      <c r="E20" s="6" t="inlineStr">
+        <is>
+          <t>20.2%</t>
+        </is>
+      </c>
+      <c r="F20" s="6" t="n"/>
+    </row>
+    <row r="21">
+      <c r="A21" s="5" t="inlineStr">
+        <is>
+          <t>Additional own funds requirements based on SREP (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B21" s="6" t="n"/>
+      <c r="C21" s="6" t="n"/>
+      <c r="D21" s="6" t="n"/>
+      <c r="E21" s="6" t="n"/>
+      <c r="F21" s="6" t="n"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="6" t="inlineStr">
+        <is>
+          <t>UK 7a  Additional CET1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B22" s="6" t="inlineStr">
+        <is>
+          <t>2.6%</t>
+        </is>
+      </c>
+      <c r="C22" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="D22" s="6" t="inlineStr">
+        <is>
+          <t>2.9%</t>
+        </is>
+      </c>
+      <c r="E22" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F22" s="6" t="n"/>
+    </row>
+    <row r="23">
+      <c r="A23" s="6" t="inlineStr">
+        <is>
+          <t>UK 7b  Additional AT1 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B23" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>0.9%</t>
+        </is>
+      </c>
+      <c r="D23" s="6" t="inlineStr">
+        <is>
+          <t>1.0%</t>
+        </is>
+      </c>
+      <c r="E23" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="F23" s="6" t="n"/>
+    </row>
+    <row r="24">
+      <c r="A24" s="6" t="inlineStr">
+        <is>
+          <t>UK 7c  Additional T2 SREP requirements (%)</t>
+        </is>
+      </c>
+      <c r="B24" s="6" t="inlineStr">
+        <is>
+          <t>1.2%</t>
+        </is>
+      </c>
+      <c r="C24" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="D24" s="6" t="inlineStr">
+        <is>
+          <t>1.3%</t>
+        </is>
+      </c>
+      <c r="E24" s="6" t="inlineStr">
+        <is>
+          <t>1.1%</t>
+        </is>
+      </c>
+      <c r="F24" s="6" t="n"/>
+    </row>
+    <row r="25">
+      <c r="A25" s="6" t="inlineStr">
+        <is>
+          <t>UK 7d  Total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B25" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="C25" s="6" t="inlineStr">
+        <is>
+          <t>13.1%</t>
+        </is>
+      </c>
+      <c r="D25" s="6" t="inlineStr">
+        <is>
+          <t>13.1%</t>
+        </is>
+      </c>
+      <c r="E25" s="6" t="inlineStr">
+        <is>
+          <t>12.5%</t>
+        </is>
+      </c>
+      <c r="F25" s="6" t="n"/>
+    </row>
+    <row r="26">
+      <c r="A26" s="5" t="inlineStr">
+        <is>
+          <t>Combined buffer requirement (as a percentage of risk-weighted exposure amount)</t>
+        </is>
+      </c>
+      <c r="B26" s="6" t="n"/>
+      <c r="C26" s="6" t="n"/>
+      <c r="D26" s="6" t="n"/>
+      <c r="E26" s="6" t="n"/>
+      <c r="F26" s="6" t="n"/>
+    </row>
+    <row r="27">
+      <c r="A27" s="6" t="inlineStr">
+        <is>
+          <t>8  Capital conservation buffer (%)</t>
+        </is>
+      </c>
+      <c r="B27" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="C27" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="D27" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="E27" s="6" t="inlineStr">
+        <is>
+          <t>2.5%</t>
+        </is>
+      </c>
+      <c r="F27" s="6" t="n"/>
+    </row>
+    <row r="28">
+      <c r="A28" s="6" t="inlineStr">
+        <is>
+          <t>9  Institution specific countercyclical capital buffer (%)</t>
+        </is>
+      </c>
+      <c r="B28" s="6" t="inlineStr">
+        <is>
+          <t>0.8%</t>
+        </is>
+      </c>
+      <c r="C28" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="D28" s="6" t="inlineStr">
+        <is>
+          <t>0.7%</t>
+        </is>
+      </c>
+      <c r="E28" s="6" t="inlineStr">
+        <is>
+          <t>0.3%</t>
+        </is>
+      </c>
+      <c r="F28" s="6" t="n"/>
+    </row>
+    <row r="29">
+      <c r="A29" s="6" t="inlineStr">
+        <is>
+          <t>11  Combined buffer requirement (%)</t>
+        </is>
+      </c>
+      <c r="B29" s="6" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="C29" s="6" t="inlineStr">
+        <is>
+          <t>3.3%</t>
+        </is>
+      </c>
+      <c r="D29" s="6" t="inlineStr">
+        <is>
+          <t>3.2%</t>
+        </is>
+      </c>
+      <c r="E29" s="6" t="inlineStr">
+        <is>
+          <t>2.8%</t>
+        </is>
+      </c>
+      <c r="F29" s="6" t="n"/>
+    </row>
+    <row r="30">
+      <c r="A30" s="6" t="inlineStr">
+        <is>
+          <t>UK 11a  Overall capital requirements (%)</t>
+        </is>
+      </c>
+      <c r="B30" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="C30" s="6" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+      <c r="D30" s="6" t="inlineStr">
+        <is>
+          <t>16.3%</t>
+        </is>
+      </c>
+      <c r="E30" s="6" t="inlineStr">
+        <is>
+          <t>15.3%</t>
+        </is>
+      </c>
+      <c r="F30" s="6" t="n"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="6" t="inlineStr">
+        <is>
+          <t>12  CET1 available after meeting the total SREP own funds requirements (%)</t>
+        </is>
+      </c>
+      <c r="B31" s="6" t="inlineStr">
+        <is>
+          <t>5.5%</t>
+        </is>
+      </c>
+      <c r="C31" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="D31" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="E31" s="6" t="inlineStr">
+        <is>
+          <t>5.7%</t>
+        </is>
+      </c>
+      <c r="F31" s="6" t="n"/>
+    </row>
+    <row r="32">
+      <c r="A32" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio - Barclays Bank PLC sub-consolidated group (the first of the two blocks printed)</t>
+        </is>
+      </c>
+      <c r="B32" s="6" t="n"/>
+      <c r="C32" s="6" t="n"/>
+      <c r="D32" s="6" t="n"/>
+      <c r="E32" s="6" t="n"/>
+      <c r="F32" s="6" t="n"/>
+    </row>
+    <row r="33">
+      <c r="A33" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excl. claims on central banks - sub-consolidated group (£m)</t>
+        </is>
+      </c>
+      <c r="B33" s="6" t="n">
+        <v>980935</v>
+      </c>
+      <c r="C33" s="6" t="n">
+        <v>946809</v>
+      </c>
+      <c r="D33" s="6" t="n">
+        <v>924826</v>
+      </c>
+      <c r="E33" s="6" t="n"/>
+      <c r="F33" s="6" t="n"/>
+    </row>
+    <row r="34">
+      <c r="A34" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%) - sub-consolidated group</t>
+        </is>
+      </c>
+      <c r="B34" s="6" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="C34" s="6" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="D34" s="6" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="E34" s="6" t="n"/>
+      <c r="F34" s="6" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a  Fully loaded ECL accounting model leverage ratio excl. central banks (%) - sub-consolidated</t>
+        </is>
+      </c>
+      <c r="B35" s="6" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="C35" s="6" t="inlineStr">
+        <is>
+          <t>5.8%</t>
+        </is>
+      </c>
+      <c r="D35" s="6" t="inlineStr">
+        <is>
+          <t>6.0%</t>
+        </is>
+      </c>
+      <c r="E35" s="6" t="n"/>
+      <c r="F35" s="6" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="6" t="inlineStr">
+        <is>
+          <t>UK 14b  Leverage ratio including claims on central banks (%) - sub-consolidated group</t>
+        </is>
+      </c>
+      <c r="B36" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="C36" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="D36" s="6" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="E36" s="6" t="n"/>
+      <c r="F36" s="6" t="n"/>
+    </row>
+    <row r="37">
+      <c r="A37" s="6" t="inlineStr">
+        <is>
+          <t>UK 14c  Average leverage ratio excluding claims on central banks (%) - sub-consolidated group</t>
+        </is>
+      </c>
+      <c r="B37" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="C37" s="6" t="inlineStr">
+        <is>
+          <t>5.2%</t>
+        </is>
+      </c>
+      <c r="D37" s="6" t="inlineStr">
+        <is>
+          <t>5.4%</t>
+        </is>
+      </c>
+      <c r="E37" s="6" t="n"/>
+      <c r="F37" s="6" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="6" t="inlineStr">
+        <is>
+          <t>UK 14d  Average leverage ratio including claims on central banks (%) - sub-consolidated group</t>
+        </is>
+      </c>
+      <c r="B38" s="6" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="C38" s="6" t="inlineStr">
+        <is>
+          <t>4.4%</t>
+        </is>
+      </c>
+      <c r="D38" s="6" t="inlineStr">
+        <is>
+          <t>4.5%</t>
+        </is>
+      </c>
+      <c r="E38" s="6" t="n"/>
+      <c r="F38" s="6" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="6" t="inlineStr">
+        <is>
+          <t>UK 14e  Countercyclical leverage ratio buffer (%) - sub-consolidated group</t>
+        </is>
+      </c>
+      <c r="B39" s="6" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="C39" s="6" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="D39" s="6" t="inlineStr">
+        <is>
+          <t>0.2%</t>
+        </is>
+      </c>
+      <c r="E39" s="6" t="n"/>
+      <c r="F39" s="6" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="5" t="inlineStr">
+        <is>
+          <t>Leverage ratio - Barclays Bank PLC solo-consolidated (the report's SECOND block; different figures)</t>
+        </is>
+      </c>
+      <c r="B40" s="6" t="n"/>
+      <c r="C40" s="6" t="n"/>
+      <c r="D40" s="6" t="n"/>
+      <c r="E40" s="6" t="n"/>
+      <c r="F40" s="6" t="n"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="6" t="inlineStr">
+        <is>
+          <t>13  Total exposure measure excl. claims on central banks - solo-consolidated (£m)</t>
+        </is>
+      </c>
+      <c r="B41" s="6" t="n">
+        <v>870620</v>
+      </c>
+      <c r="C41" s="6" t="n">
+        <v>831060</v>
+      </c>
+      <c r="D41" s="6" t="n">
+        <v>785494</v>
+      </c>
+      <c r="E41" s="6" t="n">
+        <v>742730</v>
+      </c>
+      <c r="F41" s="6" t="n"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="6" t="inlineStr">
+        <is>
+          <t>14  Leverage ratio excluding claims on central banks (%) - solo-consolidated</t>
+        </is>
+      </c>
+      <c r="B42" s="6" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="C42" s="6" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D42" s="6" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E42" s="6" t="inlineStr">
+        <is>
+          <t>4.6%</t>
+        </is>
+      </c>
+      <c r="F42" s="6" t="n"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="6" t="inlineStr">
+        <is>
+          <t>UK 14a  Fully loaded ECL accounting model leverage ratio excl. central banks (%) - solo-consolidated</t>
+        </is>
+      </c>
+      <c r="B43" s="6" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="C43" s="6" t="inlineStr">
+        <is>
+          <t>4.1%</t>
+        </is>
+      </c>
+      <c r="D43" s="6" t="inlineStr">
+        <is>
+          <t>4.3%</t>
+        </is>
+      </c>
+      <c r="E43" s="6" t="n"/>
+      <c r="F43" s="6" t="n"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="6" t="inlineStr">
+        <is>
+          <t>UK 14b  Leverage ratio including claims on central banks (%) - solo-consolidated</t>
+        </is>
+      </c>
+      <c r="B44" s="6" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="C44" s="6" t="inlineStr">
+        <is>
+          <t>3.4%</t>
+        </is>
+      </c>
+      <c r="D44" s="6" t="inlineStr">
+        <is>
+          <t>3.6%</t>
+        </is>
+      </c>
+      <c r="E44" s="6" t="n"/>
+      <c r="F44" s="6" t="n"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="5" t="inlineStr">
+        <is>
+          <t>Liquidity Coverage Ratio</t>
+        </is>
+      </c>
+      <c r="B45" s="6" t="n"/>
+      <c r="C45" s="6" t="n"/>
+      <c r="D45" s="6" t="n"/>
+      <c r="E45" s="6" t="n"/>
+      <c r="F45" s="6" t="n"/>
+    </row>
+    <row r="46">
+      <c r="A46" s="6" t="inlineStr">
+        <is>
+          <t>15  Total high-quality liquid assets (HQLA) (Weighted value) (£m)</t>
+        </is>
+      </c>
+      <c r="B46" s="6" t="n">
+        <v>222575</v>
+      </c>
+      <c r="C46" s="6" t="n">
+        <v>201875</v>
+      </c>
+      <c r="D46" s="6" t="n">
+        <v>210787</v>
+      </c>
+      <c r="E46" s="6" t="n">
+        <v>205518</v>
+      </c>
+      <c r="F46" s="6" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="6" t="inlineStr">
+        <is>
+          <t>UK 16a  Cash outflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B47" s="6" t="n">
+        <v>364579</v>
+      </c>
+      <c r="C47" s="6" t="n">
+        <v>297627</v>
+      </c>
+      <c r="D47" s="6" t="n">
+        <v>245582</v>
+      </c>
+      <c r="E47" s="6" t="n"/>
+      <c r="F47" s="6" t="n"/>
+    </row>
+    <row r="48">
+      <c r="A48" s="6" t="inlineStr">
+        <is>
+          <t>UK 16b  Cash inflows - Total weighted value (£m)</t>
+        </is>
+      </c>
+      <c r="B48" s="6" t="n">
+        <v>214872</v>
+      </c>
+      <c r="C48" s="6" t="n">
+        <v>168808</v>
+      </c>
+      <c r="D48" s="6" t="n">
+        <v>105530</v>
+      </c>
+      <c r="E48" s="6" t="n"/>
+      <c r="F48" s="6" t="n"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="6" t="inlineStr">
+        <is>
+          <t>16  Total net cash outflows (adjusted value) (£m)</t>
+        </is>
+      </c>
+      <c r="B49" s="6" t="n">
+        <v>149707</v>
+      </c>
+      <c r="C49" s="6" t="n">
+        <v>128820</v>
+      </c>
+      <c r="D49" s="6" t="n">
+        <v>140053</v>
+      </c>
+      <c r="E49" s="6" t="n">
+        <v>153542</v>
+      </c>
+      <c r="F49" s="6" t="n"/>
+    </row>
+    <row r="50">
+      <c r="A50" s="6" t="inlineStr">
+        <is>
+          <t>17  Liquidity coverage ratio (%)</t>
+        </is>
+      </c>
+      <c r="B50" s="6" t="inlineStr">
+        <is>
+          <t>149.7%</t>
+        </is>
+      </c>
+      <c r="C50" s="6" t="inlineStr">
+        <is>
+          <t>157.1%</t>
+        </is>
+      </c>
+      <c r="D50" s="6" t="inlineStr">
+        <is>
+          <t>151%</t>
+        </is>
+      </c>
+      <c r="E50" s="6" t="inlineStr">
+        <is>
+          <t>134%</t>
+        </is>
+      </c>
+      <c r="F50" s="6" t="n"/>
+    </row>
+    <row r="51">
+      <c r="A51" s="6" t="inlineStr">
+        <is>
+          <t>17a  Liquidity coverage ratio (%) (period end)</t>
+        </is>
+      </c>
+      <c r="B51" s="6" t="n"/>
+      <c r="C51" s="6" t="n"/>
+      <c r="D51" s="6" t="n"/>
+      <c r="E51" s="6" t="inlineStr">
+        <is>
+          <t>148%</t>
+        </is>
+      </c>
+      <c r="F51" s="6" t="n"/>
+    </row>
+    <row r="52">
+      <c r="A52" s="5" t="inlineStr">
+        <is>
+          <t>Net Stable Funding Ratio</t>
+        </is>
+      </c>
+      <c r="B52" s="6" t="n"/>
+      <c r="C52" s="6" t="n"/>
+      <c r="D52" s="6" t="n"/>
+      <c r="E52" s="6" t="n"/>
+      <c r="F52" s="6" t="n"/>
+    </row>
+    <row r="53">
+      <c r="A53" s="6" t="inlineStr">
+        <is>
+          <t>18  Total available stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B53" s="6" t="n">
+        <v>381301</v>
+      </c>
+      <c r="C53" s="6" t="n">
+        <v>372381</v>
+      </c>
+      <c r="D53" s="6" t="n">
+        <v>338765</v>
+      </c>
+      <c r="E53" s="6" t="n">
+        <v>309676</v>
+      </c>
+      <c r="F53" s="6" t="n"/>
+    </row>
+    <row r="54">
+      <c r="A54" s="6" t="inlineStr">
+        <is>
+          <t>19  Total required stable funding (£m)</t>
+        </is>
+      </c>
+      <c r="B54" s="6" t="n">
+        <v>336720</v>
+      </c>
+      <c r="C54" s="6" t="n">
+        <v>332874</v>
+      </c>
+      <c r="D54" s="6" t="n">
+        <v>307648</v>
+      </c>
+      <c r="E54" s="6" t="n">
+        <v>288035</v>
+      </c>
+      <c r="F54" s="6" t="n"/>
+    </row>
+    <row r="55">
+      <c r="A55" s="6" t="inlineStr">
+        <is>
+          <t>20  NSFR ratio (%)</t>
+        </is>
+      </c>
+      <c r="B55" s="6" t="inlineStr">
+        <is>
+          <t>113.3%</t>
+        </is>
+      </c>
+      <c r="C55" s="6" t="inlineStr">
+        <is>
+          <t>111.9%</t>
+        </is>
+      </c>
+      <c r="D55" s="6" t="inlineStr">
+        <is>
+          <t>110%</t>
+        </is>
+      </c>
+      <c r="E55" s="6" t="inlineStr">
+        <is>
+          <t>108%</t>
+        </is>
+      </c>
+      <c r="F55" s="6" t="n"/>
+    </row>
+    <row r="57" ht="580" customHeight="1">
+      <c r="A57" s="8" t="inlineStr">
+        <is>
+          <t>Source - Barclays Bank PLC's own dedicated Pillar 3 Reports, each year from its OWN edition's year-end column, £m:
+FY2025: Pillar 3 Report 2025, p.5 (Table 1: KM1 - Key metrics - Part 1) and p.6 (Part 2), 'As at 31.12.25' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2025Results/FY25-BBPLC-Pillar-3.pdf
+FY2024: Pillar 3 Report 2024, p.5 and p.6, 'As at 31.12.24' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/ResultAnnouncements/FullYear2024Results/FY24-Barclays-Bank-PLC-Pillar-3-Report.pdf
+FY2023: Pillar 3 Report 2023, p.5 and p.6, 'As at 31.12.23' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2023/BB-PLC-Pillar-3-Report-2023.pdf
+FY2022: Pillar 3 Report 2022, p.4 and p.5, 'As at 31.12.22' column - https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2022/Pillar-3/Barclays-Bank-PLC-Pillar-3-Report%202022.pdf
+(Page numbers above are the reports' OWN printed folios, which run one behind the PDF's sheet count - the FY2025 report carries '05' in the header of the Part 1 page and its Article 447 disclosure index reads 'Page 5 / Table 1: KM1 - Key metrics'. Cite what a reader would turn to, not the PDF page index.)
+THE COLUMNS IN THE SOURCE ARE QUARTER-ENDS, NOT YEARS - each edition prints its own 31 December followed by the three preceding quarter-ends and the prior 31 December. Only each edition's own 31 December column is used here.
+FY2021 IS BLANK, AND THAT HAS BEEN TESTED RATHER THAN ASSUMED. Barclays Bank PLC published no Pillar 3 report of its own before 2022: the Barclays annual-reports index lists Pillar 3 documents for this entity for 2022, 2023, FY24 and FY25 only (checked 2026-09-16), and two direct probes for a 2021 edition return 404. Because a subsidiary's KM1 is often published inside its parent's report, the PARENT was checked too: Barclays PLC Pillar 3 Report 2021 (257 pages, fetched and read in full) contains exactly one KM1 - 'Table 6: KM1 - Key metrics' on p.18 - and it is Barclays PLC's own. Its appendices cover the countercyclical capital buffer and remuneration; none carries a subsidiary KM1. So no Barclays Bank PLC KM1 exists for FY2021 in either the entity's own disclosures or its parent's. FY2021 capital and liquidity figures remain on the individual metric sheets, sourced from the Annual Report's Treasury and Capital risk section and cited there.
+ROWS 13 AND 14 ARE PRINTED TWICE, FOR TWO DIFFERENT ENTITIES, and the two copies differ substantially. Part 2 carries a 'Barclays Bank PLC sub-consolidated group' leverage block and then a 'Barclays Bank PLC solo-consolidated' one - at 31.12.25, exposure of £980,935m at 5.8% against £870,620m at 4.1%. Both are reproduced below under their own captions and neither is substituted for the other. Rows UK 14c/14d/14e are printed only in the sub-consolidated block. The FY2022 edition prints a single unlabelled leverage block; its figures (£742,730m, 4.6%) match the FY2023 edition's solo-consolidated 31.12.22 comparative exactly, which is why they are placed on the solo-consolidated rows here.
+EXPECTED DISAGREEMENTS WITH THIS WORKBOOK'S OWN METRIC SHEETS - all real, none a transcription slip:
+  (a) Row 14, solo-consolidated, FY2023-FY2025 (4.3% / 4.1% / 4.1%). The Leverage Ratio sheet carries the UK leverage ratio, which moved to a Barclays Bank PLC SUB-CONSOLIDATED basis from 1 January 2023 (PRA approval 20 December 2022) and so reads 6.0% / 5.8% / 5.8%. The sub-consolidated rows below match that sheet; the solo rows cannot, because they are a different basis printed in the same table.
+  (b) Row 17, FY2024: 157.1% here against 147.9% on the LCR sheet. The FY2025 edition re-presented prior-period LCR comparatives for a change to the calculation of outflows on certain secured financing transactions (its note 7). The LCR sheet deliberately adopts the re-presented 147.9% for comparability and says so; this sheet carries the FY2024 edition's own 157.1%, because each year here comes from its own edition. Both figures are correct on their own basis.
+  (c) Row 17, FY2022: 134% here against 148% on the LCR sheet. Row 17 is the 12-month average and row 17a is the period-end figure of 148%; the LCR sheet took the period-end one. Both are printed in the same table and both appear below.
+LATEST-EDITION CHECK, 2026-09-16: the Barclays annual-reports index lists 58 Pillar 3 documents; the newest for this entity is FY25-BBPLC-Pillar-3.pdf, which this workbook holds. Probes for an FY26 edition return an HTML soft-404, consistent with a 31 December year-end. None newer exists.
+ENTITY: every figure below is Barclays Bank PLC's own, on the basis its own report names in each block. No Barclays PLC (group) figure appears anywhere on this sheet.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
+  <mergeCells count="1">
+    <mergeCell ref="A57:F57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9594,14 +10801,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — CET1 Ratio</t>
+          <t>Barclays Bank PLC — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, % of RWA</t>
+          <t>Solo-consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -9640,33 +10847,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>12.9%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>28177</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>26995</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>25470</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>25907</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>23928</v>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
@@ -9715,14 +10912,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Tier 1 Capital</t>
+          <t>Barclays Bank PLC — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Solo-consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -9761,23 +10958,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 (T1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>35848</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>33787</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>33864</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>34139</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>32395</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -9581,7 +9581,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F57"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -9589,7 +9589,6 @@
     <col width="15" customWidth="1" min="3" max="3"/>
     <col width="15" customWidth="1" min="4" max="4"/>
     <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -9632,11 +9631,6 @@
           <t>FY2022</t>
         </is>
       </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
     </row>
     <row r="4">
       <c r="A4" s="5" t="inlineStr">
@@ -9648,7 +9642,6 @@
       <c r="C4" s="6" t="n"/>
       <c r="D4" s="6" t="n"/>
       <c r="E4" s="6" t="n"/>
-      <c r="F4" s="6" t="n"/>
     </row>
     <row r="5">
       <c r="A5" s="6" t="inlineStr">
@@ -9668,7 +9661,6 @@
       <c r="E5" s="6" t="n">
         <v>25907</v>
       </c>
-      <c r="F5" s="6" t="n"/>
     </row>
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
@@ -9686,7 +9678,6 @@
       <c r="E6" s="6" t="n">
         <v>25571</v>
       </c>
-      <c r="F6" s="6" t="n"/>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
@@ -9706,7 +9697,6 @@
       <c r="E7" s="6" t="n">
         <v>34139</v>
       </c>
-      <c r="F7" s="6" t="n"/>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
@@ -9724,7 +9714,6 @@
       <c r="E8" s="6" t="n">
         <v>33802</v>
       </c>
-      <c r="F8" s="6" t="n"/>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
@@ -9744,7 +9733,6 @@
       <c r="E9" s="6" t="n">
         <v>42321</v>
       </c>
-      <c r="F9" s="6" t="n"/>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
@@ -9762,7 +9750,6 @@
       <c r="E10" s="6" t="n">
         <v>41092</v>
       </c>
-      <c r="F10" s="6" t="n"/>
     </row>
     <row r="11">
       <c r="A11" s="5" t="inlineStr">
@@ -9774,7 +9761,6 @@
       <c r="C11" s="6" t="n"/>
       <c r="D11" s="6" t="n"/>
       <c r="E11" s="6" t="n"/>
-      <c r="F11" s="6" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -9794,7 +9780,6 @@
       <c r="E12" s="6" t="n">
         <v>203833</v>
       </c>
-      <c r="F12" s="6" t="n"/>
     </row>
     <row r="13">
       <c r="A13" s="6" t="inlineStr">
@@ -9812,7 +9797,6 @@
       <c r="E13" s="6" t="n">
         <v>203531</v>
       </c>
-      <c r="F13" s="6" t="n"/>
     </row>
     <row r="14">
       <c r="A14" s="5" t="inlineStr">
@@ -9824,7 +9808,6 @@
       <c r="C14" s="6" t="n"/>
       <c r="D14" s="6" t="n"/>
       <c r="E14" s="6" t="n"/>
-      <c r="F14" s="6" t="n"/>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
@@ -9852,7 +9835,6 @@
           <t>12.7%</t>
         </is>
       </c>
-      <c r="F15" s="6" t="n"/>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
@@ -9876,7 +9858,6 @@
           <t>12.6%</t>
         </is>
       </c>
-      <c r="F16" s="6" t="n"/>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
@@ -9904,7 +9885,6 @@
           <t>16.7%</t>
         </is>
       </c>
-      <c r="F17" s="6" t="n"/>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
@@ -9928,7 +9908,6 @@
           <t>16.6%</t>
         </is>
       </c>
-      <c r="F18" s="6" t="n"/>
     </row>
     <row r="19">
       <c r="A19" s="6" t="inlineStr">
@@ -9956,7 +9935,6 @@
           <t>20.8%</t>
         </is>
       </c>
-      <c r="F19" s="6" t="n"/>
     </row>
     <row r="20">
       <c r="A20" s="6" t="inlineStr">
@@ -9980,7 +9958,6 @@
           <t>20.2%</t>
         </is>
       </c>
-      <c r="F20" s="6" t="n"/>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -9992,7 +9969,6 @@
       <c r="C21" s="6" t="n"/>
       <c r="D21" s="6" t="n"/>
       <c r="E21" s="6" t="n"/>
-      <c r="F21" s="6" t="n"/>
     </row>
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
@@ -10020,7 +9996,6 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="F22" s="6" t="n"/>
     </row>
     <row r="23">
       <c r="A23" s="6" t="inlineStr">
@@ -10048,7 +10023,6 @@
           <t>0.8%</t>
         </is>
       </c>
-      <c r="F23" s="6" t="n"/>
     </row>
     <row r="24">
       <c r="A24" s="6" t="inlineStr">
@@ -10076,7 +10050,6 @@
           <t>1.1%</t>
         </is>
       </c>
-      <c r="F24" s="6" t="n"/>
     </row>
     <row r="25">
       <c r="A25" s="6" t="inlineStr">
@@ -10104,7 +10077,6 @@
           <t>12.5%</t>
         </is>
       </c>
-      <c r="F25" s="6" t="n"/>
     </row>
     <row r="26">
       <c r="A26" s="5" t="inlineStr">
@@ -10116,7 +10088,6 @@
       <c r="C26" s="6" t="n"/>
       <c r="D26" s="6" t="n"/>
       <c r="E26" s="6" t="n"/>
-      <c r="F26" s="6" t="n"/>
     </row>
     <row r="27">
       <c r="A27" s="6" t="inlineStr">
@@ -10144,7 +10115,6 @@
           <t>2.5%</t>
         </is>
       </c>
-      <c r="F27" s="6" t="n"/>
     </row>
     <row r="28">
       <c r="A28" s="6" t="inlineStr">
@@ -10172,7 +10142,6 @@
           <t>0.3%</t>
         </is>
       </c>
-      <c r="F28" s="6" t="n"/>
     </row>
     <row r="29">
       <c r="A29" s="6" t="inlineStr">
@@ -10200,7 +10169,6 @@
           <t>2.8%</t>
         </is>
       </c>
-      <c r="F29" s="6" t="n"/>
     </row>
     <row r="30">
       <c r="A30" s="6" t="inlineStr">
@@ -10228,7 +10196,6 @@
           <t>15.3%</t>
         </is>
       </c>
-      <c r="F30" s="6" t="n"/>
     </row>
     <row r="31">
       <c r="A31" s="6" t="inlineStr">
@@ -10256,7 +10223,6 @@
           <t>5.7%</t>
         </is>
       </c>
-      <c r="F31" s="6" t="n"/>
     </row>
     <row r="32">
       <c r="A32" s="5" t="inlineStr">
@@ -10268,7 +10234,6 @@
       <c r="C32" s="6" t="n"/>
       <c r="D32" s="6" t="n"/>
       <c r="E32" s="6" t="n"/>
-      <c r="F32" s="6" t="n"/>
     </row>
     <row r="33">
       <c r="A33" s="6" t="inlineStr">
@@ -10286,7 +10251,6 @@
         <v>924826</v>
       </c>
       <c r="E33" s="6" t="n"/>
-      <c r="F33" s="6" t="n"/>
     </row>
     <row r="34">
       <c r="A34" s="6" t="inlineStr">
@@ -10310,7 +10274,6 @@
         </is>
       </c>
       <c r="E34" s="6" t="n"/>
-      <c r="F34" s="6" t="n"/>
     </row>
     <row r="35">
       <c r="A35" s="6" t="inlineStr">
@@ -10334,7 +10297,6 @@
         </is>
       </c>
       <c r="E35" s="6" t="n"/>
-      <c r="F35" s="6" t="n"/>
     </row>
     <row r="36">
       <c r="A36" s="6" t="inlineStr">
@@ -10358,7 +10320,6 @@
         </is>
       </c>
       <c r="E36" s="6" t="n"/>
-      <c r="F36" s="6" t="n"/>
     </row>
     <row r="37">
       <c r="A37" s="6" t="inlineStr">
@@ -10382,7 +10343,6 @@
         </is>
       </c>
       <c r="E37" s="6" t="n"/>
-      <c r="F37" s="6" t="n"/>
     </row>
     <row r="38">
       <c r="A38" s="6" t="inlineStr">
@@ -10406,7 +10366,6 @@
         </is>
       </c>
       <c r="E38" s="6" t="n"/>
-      <c r="F38" s="6" t="n"/>
     </row>
     <row r="39">
       <c r="A39" s="6" t="inlineStr">
@@ -10430,7 +10389,6 @@
         </is>
       </c>
       <c r="E39" s="6" t="n"/>
-      <c r="F39" s="6" t="n"/>
     </row>
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
@@ -10442,7 +10400,6 @@
       <c r="C40" s="6" t="n"/>
       <c r="D40" s="6" t="n"/>
       <c r="E40" s="6" t="n"/>
-      <c r="F40" s="6" t="n"/>
     </row>
     <row r="41">
       <c r="A41" s="6" t="inlineStr">
@@ -10462,7 +10419,6 @@
       <c r="E41" s="6" t="n">
         <v>742730</v>
       </c>
-      <c r="F41" s="6" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="6" t="inlineStr">
@@ -10490,7 +10446,6 @@
           <t>4.6%</t>
         </is>
       </c>
-      <c r="F42" s="6" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="6" t="inlineStr">
@@ -10514,7 +10469,6 @@
         </is>
       </c>
       <c r="E43" s="6" t="n"/>
-      <c r="F43" s="6" t="n"/>
     </row>
     <row r="44">
       <c r="A44" s="6" t="inlineStr">
@@ -10538,7 +10492,6 @@
         </is>
       </c>
       <c r="E44" s="6" t="n"/>
-      <c r="F44" s="6" t="n"/>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
@@ -10550,7 +10503,6 @@
       <c r="C45" s="6" t="n"/>
       <c r="D45" s="6" t="n"/>
       <c r="E45" s="6" t="n"/>
-      <c r="F45" s="6" t="n"/>
     </row>
     <row r="46">
       <c r="A46" s="6" t="inlineStr">
@@ -10570,7 +10522,6 @@
       <c r="E46" s="6" t="n">
         <v>205518</v>
       </c>
-      <c r="F46" s="6" t="n"/>
     </row>
     <row r="47">
       <c r="A47" s="6" t="inlineStr">
@@ -10588,7 +10539,6 @@
         <v>245582</v>
       </c>
       <c r="E47" s="6" t="n"/>
-      <c r="F47" s="6" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="6" t="inlineStr">
@@ -10606,7 +10556,6 @@
         <v>105530</v>
       </c>
       <c r="E48" s="6" t="n"/>
-      <c r="F48" s="6" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="6" t="inlineStr">
@@ -10626,7 +10575,6 @@
       <c r="E49" s="6" t="n">
         <v>153542</v>
       </c>
-      <c r="F49" s="6" t="n"/>
     </row>
     <row r="50">
       <c r="A50" s="6" t="inlineStr">
@@ -10654,7 +10602,6 @@
           <t>134%</t>
         </is>
       </c>
-      <c r="F50" s="6" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="6" t="inlineStr">
@@ -10670,7 +10617,6 @@
           <t>148%</t>
         </is>
       </c>
-      <c r="F51" s="6" t="n"/>
     </row>
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
@@ -10682,7 +10628,6 @@
       <c r="C52" s="6" t="n"/>
       <c r="D52" s="6" t="n"/>
       <c r="E52" s="6" t="n"/>
-      <c r="F52" s="6" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="6" t="inlineStr">
@@ -10702,7 +10647,6 @@
       <c r="E53" s="6" t="n">
         <v>309676</v>
       </c>
-      <c r="F53" s="6" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="6" t="inlineStr">
@@ -10722,7 +10666,6 @@
       <c r="E54" s="6" t="n">
         <v>288035</v>
       </c>
-      <c r="F54" s="6" t="n"/>
     </row>
     <row r="55">
       <c r="A55" s="6" t="inlineStr">
@@ -10750,7 +10693,6 @@
           <t>108%</t>
         </is>
       </c>
-      <c r="F55" s="6" t="n"/>
     </row>
     <row r="57" ht="580" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
@@ -10775,7 +10717,7 @@
     </row>
   </sheetData>
   <mergeCells count="1">
-    <mergeCell ref="A57:F57"/>
+    <mergeCell ref="A57:E57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -1730,6 +1730,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -4347,14 +4348,14 @@
       </c>
       <c r="F6" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not applicable – UK NSFR requirement began 1 Jan 2022; BBPLC Annual Report 2021 names the NSFR only as a forthcoming standard, with no figure (checked 2026-09-19)</t>
         </is>
       </c>
     </row>
     <row r="7" ht="60" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
-          <t>Note: NSFR is an average of the last four spot quarter-end ratios. It was not a UK regulatory requirement as at FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2021 figure is available.</t>
+          <t>Note: GA-020 (2026-09-19): the FY2021 cell was checked against Barclays Bank PLC's own Annual Report 2021 (https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-PLC-2021-AR.pdf): its only two NSFR mentions describe the NSFR as a forthcoming Basel III standard, with no figure; no FY2021 Barclays Bank PLC Pillar 3 is listed on the Bank's annual-reports index. NSFR is an average of the last four spot quarter-end ratios. It was not a UK regulatory requirement as at FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2021 figure is available.</t>
         </is>
       </c>
     </row>
@@ -4444,34 +4445,34 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – this year's BBPLC Pillar 3 Art. 437a row: 'MREL disclosures are not applicable for Barclays Bank PLC' (refers to Barclays PLC TLAC2); annual report gives Group MREL only</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – this year's BBPLC Pillar 3 Art. 437a row: 'MREL disclosures are not applicable for Barclays Bank PLC' (refers to Barclays PLC TLAC2); annual report gives Group MREL only</t>
         </is>
       </c>
       <c r="D4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no BBPLC MREL ratio in its annual report (MREL described at Barclays Group level only) or Pillar 3 (full-text search 2026-09-19)</t>
         </is>
       </c>
       <c r="E4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no BBPLC MREL ratio in its annual report (MREL described at Barclays Group level only) or Pillar 3 (full-text search 2026-09-19)</t>
         </is>
       </c>
       <c r="F4" s="6" t="inlineStr">
         <is>
-          <t>Not publicly disclosed</t>
+          <t>Not published – no BBPLC MREL ratio in its Annual Report 2021 (MREL described at Barclays Group level only; full-text search 2026-09-19)</t>
         </is>
       </c>
     </row>
     <row r="5" ht="60" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: MREL (Minimum Requirement for own funds and Eligible Liabilities) is set and disclosed at the Barclays PLC resolution-group level, not for Barclays Bank PLC as an individual operating subsidiary. No MREL ratio for Barclays Bank PLC specifically was found in its Annual Reports for FY2021-FY2025.</t>
+          <t>Note: MREL (Minimum Requirement for own funds and Eligible Liabilities) is set and disclosed at the Barclays PLC resolution-group level, not for Barclays Bank PLC as an individual operating subsidiary. No MREL ratio for Barclays Bank PLC specifically was found in its Annual Reports for FY2021-FY2025. GA-020 re-check 2026-09-19: the BBPLC Annual Reports 2021-2025 (home.barclays annual-reports index) describe TLAC/MREL at Barclays Group level and give Group requirements only; the BBPLC Pillar 3 Reports 2024 (PDF p.59) and 2025 (PDF p.55) state under Art. 437a 'MREL disclosures are not applicable for Barclays Bank PLC', pointing to TLAC2 in the Barclays PLC Pillar 3 (creditor ranking, not a ratio); the 2022 and 2023 editions have no MREL text.</t>
         </is>
       </c>
     </row>

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -116,7 +116,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
@@ -2972,7 +2972,7 @@
         </is>
       </c>
     </row>
-    <row r="40" ht="45" customHeight="1">
+    <row r="40" ht="30" customHeight="1">
       <c r="A40" s="7" t="inlineStr">
         <is>
           <t>Note: Figures are duplicated from the detail sheets for at-a-glance trend viewing; see each sheet's own source citation for the underlying document/page. FY2021 capital figures are restated (Over-issuance of Securities matter). Leverage ratio basis changes year-on-year (see Leverage Ratio sheet).</t>
@@ -3073,14 +3073,14 @@
         <v>32395</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -3194,14 +3194,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -3305,14 +3305,14 @@
         <v>37954</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -3426,14 +3426,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -3537,14 +3537,14 @@
         <v>185467</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="39" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -3888,7 +3888,7 @@
         <v>185467</v>
       </c>
     </row>
-    <row r="21" ht="240" customHeight="1">
+    <row r="21" ht="299" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC's own dedicated Pillar 3 Reports (solo-consolidated basis, matching the Total RWAs sheet's own basis and figures every year below - confirmed by cross-checking each year's Total row against the Total RWAs sheet), not the Annual Report's Capital risk section (which discloses only the aggregate Total RWAs figure and capital ratios, no category breakdown):
@@ -3915,7 +3915,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F9"/>
+  <dimension ref="A1:F12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="44" customWidth="1" min="1" max="1"/>
@@ -4048,15 +4048,93 @@
         <v>883371</v>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
-      <c r="A7" s="7" t="inlineStr">
-        <is>
-          <t>Note: Basis changes across the period: FY2021 is a CRR leverage ratio (Barclays Bank PLC was not subject to the UK leverage framework until 1 January 2022; the UK-framework equivalent was disclosed as 4.1%, £767.6bn exposure). FY2022 is a UK leverage ratio on a solo-consolidated basis. From FY2023 onward, leverage minimum requirements — and the disclosed ratio — moved to a Barclays Bank PLC sub-consolidated basis (PRA approval granted 20 December 2022, effective 1 January 2023). These bases are not directly comparable year-on-year.</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="100" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Total exposure measure including claims on central banks (£m)</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="n">
+        <v>1191554</v>
+      </c>
+      <c r="C7" s="6" t="n">
+        <v>1136468</v>
+      </c>
+      <c r="D7" s="6" t="n">
+        <v>1123447</v>
+      </c>
+      <c r="E7" s="6" t="n">
+        <v>923576</v>
+      </c>
+      <c r="F7" s="6" t="n"/>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Claims on central banks excluded (£m)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="n">
+        <v>-210619</v>
+      </c>
+      <c r="C8" s="6" t="n">
+        <v>-189659</v>
+      </c>
+      <c r="D8" s="6" t="n">
+        <v>-198621</v>
+      </c>
+      <c r="E8" s="6" t="n">
+        <v>-180846</v>
+      </c>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Leverage ratio including claims on central banks (%)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>4.7%</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>4.8%</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="inlineStr">
+        <is>
+          <t>4.9%</t>
+        </is>
+      </c>
+      <c r="E9" s="6" t="inlineStr">
+        <is>
+          <t>3.7%</t>
+        </is>
+      </c>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="364" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Note: BOTH LEVERAGE BASES NOW CARRIED, FY2022-FY2025 - ADDED 2026-10-09 (GA-026). Template UK LR2 (LRCom) prints BOTH measures: row 24 and UK-25c on the INCLUDING-claims-on-central-banks basis, UK-24b and 25 on the EXCLUDING basis, with the reconciling deduction at UK-24a. The first three rows above are the EXCLUDING side; the three new rows are the including side.
+THE INCLUDING ROWS FOLLOW THE SAME ENTITY BASIS AS THE EXCLUDING ONES, YEAR BY YEAR - they have to, or the sheet would compare two different entities down one column. Each edition prints the LR2 TWICE, once for 'Barclays Bank PLC sub-consolidated' and once for 'Barclays Bank PLC solo-consolidated', and the two differ substantially. FY2023-FY2025 are taken from the SUB-CONSOLIDATED block and FY2022 from the solo-consolidated one, exactly as the existing rows are, because the disclosed UK leverage ratio moved to a sub-consolidated basis on 1 January 2023 (PRA approval 20 December 2022). See the basis-change note below, which already governs the excluding rows.
+EACH YEAR FROM ITS OWN EDITION, read at 300 dpi:
+  FY2025 - FY25 BBPLC Pillar 3, p.16, sub-consolidated, 31.12.25: row 24 1,191,554; UK-24a (210,619); UK-24b 980,935; row 25 5.8%; UK-25c 4.7%.
+  FY2024 - FY24 BBPLC Pillar 3, p.17, sub-consolidated, 31 December 2024: row 24 1,136,468; UK-24a (189,659); UK-24b 946,809; row 25 5.8%; UK-25c 4.8%.
+  FY2023 - BB PLC Pillar 3 2023, p.17, sub-consolidated, 31 December 2023: row 24 1,123,447; UK-24a (198,621); UK-24b 924,826; row 25 6.0%; UK-25c 4.9%. That block carries NO comparative - its own note b says 'No comparatives are provided for Barclays Bank PLC sub-consolidated group given this is the first reporting year.'
+  FY2022 - BB PLC Pillar 3 2022, p.16, the single unlabelled block, 31 December 2022: row 24 923,576; UK-24a (180,846); UK-24b 742,730; row 25 4.6%; UK-25c 3.7%. It likewise carries no comparative (its note b: 'No comparatives are provided as this reflects disclosure requirements under the UKLRF from 1 January 2022'). That block is solo-consolidated: its figures equal the FY2023 edition's solo-consolidated 31.12.22 comparative column in every row, which is how it was identified.
+CHECKS RUN BEFORE TRANSCRIBING. (1) ENTITY/BASIS: UK-24b reproduces the figure the 'UK leverage exposure' row already carried in all four years (980,935 / 946,809 / 924,826 / 742,730), so each including figure sits beside an excluding figure struck on the same entity. (2) CROSS-EDITION: every comparative equals the next edition's own-year column to the last digit, on the matching basis. (3) ARITHMETIC: row 24 minus UK-24a equals UK-24b in all four years. (4) RATIO TIE: row 23 over each exposure measure reproduces both printed ratios in all four years (e.g. FY2025 56,465/1,191,554 = 4.74% -&gt; 4.7%, 56,465/980,935 = 5.76% -&gt; 5.8%).
+FY2021 CORRECTLY GETS NO INCLUDING-BASIS FIGURE: Barclays Bank PLC was not subject to the UK leverage framework until 1 January 2022, so no LR2 exists for it and the dual basis did not yet apply. Nothing is back-solved for that year.
+AVERAGE ROWS DELIBERATELY NOT USED. Each LR2 also prints UK-31/UK-32/UK-33/UK-34, the AVERAGE exposure measures and ratios (FY2025: 1,315,061 / 1,093,000 / 4.3% / 5.2%). Those are a different measure from the period-end rows this sheet carries and are not mixed into the same row.
+Basis changes across the period: FY2021 is a CRR leverage ratio (Barclays Bank PLC was not subject to the UK leverage framework until 1 January 2022; the UK-framework equivalent was disclosed as 4.1%, £767.6bn exposure). FY2022 is a UK leverage ratio on a solo-consolidated basis. From FY2023 onward, leverage minimum requirements — and the disclosed ratio — moved to a Barclays Bank PLC sub-consolidated basis (PRA approval granted 20 December 2022, effective 1 January 2023). These bases are not directly comparable year-on-year.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="117" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
 FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
@@ -4067,8 +4145,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A7:F7"/>
-    <mergeCell ref="A9:F9"/>
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -4191,14 +4269,14 @@
         </is>
       </c>
     </row>
-    <row r="6" ht="60" customHeight="1">
+    <row r="6" ht="52" customHeight="1">
       <c r="A6" s="7" t="inlineStr">
         <is>
           <t>Note: LCR is an average of the last 12 spot month-end ratios for the Barclays Bank PLC Domestic Liquidity Sub-Group (DoLSub, comprising Barclays Bank PLC and Barclays Capital Securities Limited). Barclays prospectively changed its methodology for calculating net stress outflows on secured financing transactions from June 2025; the FY2025 Annual Report re-presents FY2024 on the new basis (147.9%, used here for comparability) — the FY2024 Annual Report originally reported FY2024 LCR as 157% (FY2023 comparator in that report: 151%, unchanged).</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="100" customHeight="1">
+    <row r="8" ht="117" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -4352,14 +4430,14 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="60" customHeight="1">
+    <row r="7" ht="65" customHeight="1">
       <c r="A7" s="7" t="inlineStr">
         <is>
           <t>Note: GA-020 (2026-09-19): the FY2021 cell was checked against Barclays Bank PLC's own Annual Report 2021 (https://home.barclays/content/dam/home-barclays/documents/investor-relations/reports-and-events/annual-reports/2021/Barclays-Bank-PLC-2021-AR.pdf): its only two NSFR mentions describe the NSFR as a forthcoming Basel III standard, with no figure; no FY2021 Barclays Bank PLC Pillar 3 is listed on the Bank's annual-reports index. NSFR is an average of the last four spot quarter-end ratios. It was not a UK regulatory requirement as at FY2021 (the UK NSFR regime took effect from 1 January 2022), so no FY2021 figure is available.</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="100" customHeight="1">
+    <row r="9" ht="117" customHeight="1">
       <c r="A9" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -4469,7 +4547,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="65" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: MREL (Minimum Requirement for own funds and Eligible Liabilities) is set and disclosed at the Barclays PLC resolution-group level, not for Barclays Bank PLC as an individual operating subsidiary. No MREL ratio for Barclays Bank PLC specifically was found in its Annual Reports for FY2021-FY2025. GA-020 re-check 2026-09-19: the BBPLC Annual Reports 2021-2025 (home.barclays annual-reports index) describe TLAC/MREL at Barclays Group level and give Group requirements only; the BBPLC Pillar 3 Reports 2024 (PDF p.59) and 2025 (PDF p.55) state under Art. 437a 'MREL disclosures are not applicable for Barclays Bank PLC', pointing to TLAC2 in the Barclays PLC Pillar 3 (creditor ranking, not a ratio); the 2022 and 2023 editions have no MREL text.</t>
@@ -9090,7 +9168,7 @@
         <v>185860</v>
       </c>
     </row>
-    <row r="57" ht="100" customHeight="1">
+    <row r="57" ht="104" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC (the non ring-fenced bank; company no. 01026167) consolidated cash flow statement, £m, as filed with Companies House:
@@ -9557,7 +9635,7 @@
         </is>
       </c>
     </row>
-    <row r="23" ht="220" customHeight="1">
+    <row r="23" ht="234" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
           <t>ASSET QUALITY NOTE - IFRS 9 stage breakdown from the 'Credit risk' section of the Risk review (Loans and advances at amortised cost, audited), each Annual Report's own tables, closing (31 December) balances only:
@@ -9582,7 +9660,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="96" customWidth="1" min="1" max="1"/>
@@ -10695,7 +10773,7 @@
         </is>
       </c>
     </row>
-    <row r="57" ht="580" customHeight="1">
+    <row r="57" ht="409" customHeight="1">
       <c r="A57" s="8" t="inlineStr">
         <is>
           <t>Source - Barclays Bank PLC's own dedicated Pillar 3 Reports, each year from its OWN edition's year-end column, £m:
@@ -10708,8 +10786,15 @@
 FY2021 IS BLANK, AND THAT HAS BEEN TESTED RATHER THAN ASSUMED. Barclays Bank PLC published no Pillar 3 report of its own before 2022: the Barclays annual-reports index lists Pillar 3 documents for this entity for 2022, 2023, FY24 and FY25 only (checked 2026-09-16), and two direct probes for a 2021 edition return 404. Because a subsidiary's KM1 is often published inside its parent's report, the PARENT was checked too: Barclays PLC Pillar 3 Report 2021 (257 pages, fetched and read in full) contains exactly one KM1 - 'Table 6: KM1 - Key metrics' on p.18 - and it is Barclays PLC's own. Its appendices cover the countercyclical capital buffer and remuneration; none carries a subsidiary KM1. So no Barclays Bank PLC KM1 exists for FY2021 in either the entity's own disclosures or its parent's. FY2021 capital and liquidity figures remain on the individual metric sheets, sourced from the Annual Report's Treasury and Capital risk section and cited there.
 ROWS 13 AND 14 ARE PRINTED TWICE, FOR TWO DIFFERENT ENTITIES, and the two copies differ substantially. Part 2 carries a 'Barclays Bank PLC sub-consolidated group' leverage block and then a 'Barclays Bank PLC solo-consolidated' one - at 31.12.25, exposure of £980,935m at 5.8% against £870,620m at 4.1%. Both are reproduced below under their own captions and neither is substituted for the other. Rows UK 14c/14d/14e are printed only in the sub-consolidated block. The FY2022 edition prints a single unlabelled leverage block; its figures (£742,730m, 4.6%) match the FY2023 edition's solo-consolidated 31.12.22 comparative exactly, which is why they are placed on the solo-consolidated rows here.
 EXPECTED DISAGREEMENTS WITH THIS WORKBOOK'S OWN METRIC SHEETS - all real, none a transcription slip:
-  (a) Row 14, solo-consolidated, FY2023-FY2025 (4.3% / 4.1% / 4.1%). The Leverage Ratio sheet carries the UK leverage ratio, which moved to a Barclays Bank PLC SUB-CONSOLIDATED basis from 1 January 2023 (PRA approval 20 December 2022) and so reads 6.0% / 5.8% / 5.8%. The sub-consolidated rows below match that sheet; the solo rows cannot, because they are a different basis printed in the same table.
-  (b) Row 17, FY2024: 157.1% here against 147.9% on the LCR sheet. The FY2025 edition re-presented prior-period LCR comparatives for a change to the calculation of outflows on certain secured financing transactions (its note 7). The LCR sheet deliberately adopts the re-presented 147.9% for comparability and says so; this sheet carries the FY2024 edition's own 157.1%, because each year here comes from its own edition. Both figures are correct on their own basis.
+  (a) Row 14, solo-consolidated, FY2023-FY2025 (4.3% / 4.1% / 4.1%). The Leverage Ratio sheet carries the UK leverage ratio, which moved to a Barclays Bank PLC SUB-CONSOLIDATED basis from 1 January 2023 (PRA approval 20 December 2022) and so reads 6.0% / 5.8% / 5.8%. The sub-consolidated rows below match that sheet; the solo rows cannot, because they are a different basis printed in the same table.</t>
+        </is>
+      </c>
+    </row>
+    <row r="59" ht="409" customHeight="1">
+      <c r="A59" s="8" t="inlineStr">
+        <is>
+          <t>(continued)
+(b) Row 17, FY2024: 157.1% here against 147.9% on the LCR sheet. The FY2025 edition re-presented prior-period LCR comparatives for a change to the calculation of outflows on certain secured financing transactions (its note 7). The LCR sheet deliberately adopts the re-presented 147.9% for comparability and says so; this sheet carries the FY2024 edition's own 157.1%, because each year here comes from its own edition. Both figures are correct on their own basis.
   (c) Row 17, FY2022: 134% here against 148% on the LCR sheet. Row 17 is the 12-month average and row 17a is the period-end figure of 148%; the LCR sheet took the period-end one. Both are printed in the same table and both appear below.
 LATEST-EDITION CHECK, 2026-09-16: the Barclays annual-reports index lists 58 Pillar 3 documents; the newest for this entity is FY25-BBPLC-Pillar-3.pdf, which this workbook holds. Probes for an FY26 edition return an HTML soft-404, consistent with a 31 December year-end. None newer exists.
 ENTITY: every figure below is Barclays Bank PLC's own, on the basis its own report names in each block. No Barclays PLC (group) figure appears anywhere on this sheet.</t>
@@ -10717,7 +10802,8 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
+  <mergeCells count="2">
+    <mergeCell ref="A59:E59"/>
     <mergeCell ref="A57:E57"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -10809,14 +10895,14 @@
         <v>23928</v>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
@@ -10930,14 +11016,14 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="60" customHeight="1">
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
           <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="100" customHeight="1">
+    <row r="7" ht="117" customHeight="1">
       <c r="A7" s="8" t="inlineStr">
         <is>
           <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:

--- a/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
+++ b/banks/BARCLAYS BANK PLC FINANCIALS.xlsx
@@ -13,19 +13,20 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Statement of Changes in Equity" sheetId="4" state="visible" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Cash Flow Statement" sheetId="5" state="visible" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Asset Quality" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Profitability" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="KM1 Key Metrics" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Capital" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="CET1 Ratio" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Capital" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Tier 1 Ratio" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total Capital Ratio" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Total RWAs" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="RWA Breakdown" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Leverage Ratio" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="LCR" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="NSFR" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="MREL Ratio" sheetId="20" state="visible" r:id="rId20"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -3008,14 +3009,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Tier 1 Capital</t>
+          <t>Barclays Bank PLC — CET1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Solo-consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3054,23 +3055,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 (T1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>35848</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>33787</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>33864</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>34139</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>32395</v>
+          <t>Common Equity Tier 1 (CET1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>12.1%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>12.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>12.9%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -3119,14 +3130,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Tier 1 Ratio</t>
+          <t>Barclays Bank PLC — Tier 1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, % of RWA</t>
+          <t>Solo-consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3165,33 +3176,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Tier 1 (T1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>16.1%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>15.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>16.0%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>16.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>17.5%</t>
-        </is>
+          <t>Tier 1 (T1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>35848</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>33787</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>33864</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>34139</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>32395</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -3240,14 +3241,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total Capital</t>
+          <t>Barclays Bank PLC — Tier 1 Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Solo-consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3286,23 +3287,33 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>42129</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>40444</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>40530</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>42321</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>37954</v>
+          <t>Tier 1 (T1) ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>16.1%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>15.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>16.0%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>16.7%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>17.5%</t>
+        </is>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -3351,14 +3362,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total Capital Ratio</t>
+          <t>Barclays Bank PLC — Total Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, % of RWA</t>
+          <t>Solo-consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -3397,33 +3408,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total regulatory capital ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>19.0%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>18.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>19.2%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>20.8%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>20.5%</t>
-        </is>
+          <t>Total regulatory capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>42129</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>40444</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>40530</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>42321</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>37954</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
@@ -3472,14 +3473,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — Total RWAs</t>
+          <t>Barclays Bank PLC — Total Capital Ratio</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, £m</t>
+          <t>Solo-consolidated basis, % of RWA</t>
         </is>
       </c>
     </row>
@@ -3518,29 +3519,39 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Total risk weighted assets (RWAs)</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>222247</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>223648</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>211193</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>203833</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>185467</v>
-      </c>
-    </row>
-    <row r="5" ht="39" customHeight="1">
+          <t>Total regulatory capital ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>19.0%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>18.1%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>19.2%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>20.8%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>20.5%</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="30" customHeight="1">
       <c r="A5" s="7" t="inlineStr">
         <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
         </is>
       </c>
     </row>
@@ -3564,6 +3575,117 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="44" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Total RWAs</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Solo-consolidated basis, £m</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Total risk weighted assets (RWAs)</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>222247</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>223648</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>211193</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>203833</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>185467</v>
+      </c>
+    </row>
+    <row r="5" ht="39" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report. FY2024 comparative in the FY2025 Annual Report is calculated applying UK CRR transitional arrangements (IFRS 9 transitional relief and grandfathering of certain capital instruments), which ceased to apply from 1 January/29 June 2025.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="117" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -3909,7 +4031,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4152,7 +4274,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4295,7 +4417,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
@@ -4451,123 +4573,6 @@
   <mergeCells count="2">
     <mergeCell ref="A7:F7"/>
     <mergeCell ref="A9:F9"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="46" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank PLC — MREL Ratio</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>MREL Ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – this year's BBPLC Pillar 3 Art. 437a row: 'MREL disclosures are not applicable for Barclays Bank PLC' (refers to Barclays PLC TLAC2); annual report gives Group MREL only</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – this year's BBPLC Pillar 3 Art. 437a row: 'MREL disclosures are not applicable for Barclays Bank PLC' (refers to Barclays PLC TLAC2); annual report gives Group MREL only</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no BBPLC MREL ratio in its annual report (MREL described at Barclays Group level only) or Pillar 3 (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no BBPLC MREL ratio in its annual report (MREL described at Barclays Group level only) or Pillar 3 (full-text search 2026-09-19)</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>Not published – no BBPLC MREL ratio in its Annual Report 2021 (MREL described at Barclays Group level only; full-text search 2026-09-19)</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="65" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: MREL (Minimum Requirement for own funds and Eligible Liabilities) is set and disclosed at the Barclays PLC resolution-group level, not for Barclays Bank PLC as an individual operating subsidiary. No MREL ratio for Barclays Bank PLC specifically was found in its Annual Reports for FY2021-FY2025. GA-020 re-check 2026-09-19: the BBPLC Annual Reports 2021-2025 (home.barclays annual-reports index) describe TLAC/MREL at Barclays Group level and give Group requirements only; the BBPLC Pillar 3 Reports 2024 (PDF p.59) and 2025 (PDF p.55) state under Art. 437a 'MREL disclosures are not applicable for Barclays Bank PLC', pointing to TLAC2 in the Barclays PLC Pillar 3 (creditor ranking, not a ratio); the 2022 and 2023 editions have no MREL text.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="150" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -5592,6 +5597,123 @@
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="A51:F51"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:F7"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="46" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — MREL Ratio</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr"/>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>MREL Ratio</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – this year's BBPLC Pillar 3 Art. 437a row: 'MREL disclosures are not applicable for Barclays Bank PLC' (refers to Barclays PLC TLAC2); annual report gives Group MREL only</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – this year's BBPLC Pillar 3 Art. 437a row: 'MREL disclosures are not applicable for Barclays Bank PLC' (refers to Barclays PLC TLAC2); annual report gives Group MREL only</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no BBPLC MREL ratio in its annual report (MREL described at Barclays Group level only) or Pillar 3 (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no BBPLC MREL ratio in its annual report (MREL described at Barclays Group level only) or Pillar 3 (full-text search 2026-09-19)</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="inlineStr">
+        <is>
+          <t>Not published – no BBPLC MREL ratio in its Annual Report 2021 (MREL described at Barclays Group level only; full-text search 2026-09-19)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="65" customHeight="1">
+      <c r="A5" s="7" t="inlineStr">
+        <is>
+          <t>Note: MREL (Minimum Requirement for own funds and Eligible Liabilities) is set and disclosed at the Barclays PLC resolution-group level, not for Barclays Bank PLC as an individual operating subsidiary. No MREL ratio for Barclays Bank PLC specifically was found in its Annual Reports for FY2021-FY2025. GA-020 re-check 2026-09-19: the BBPLC Annual Reports 2021-2025 (home.barclays annual-reports index) describe TLAC/MREL at Barclays Group level and give Group requirements only; the BBPLC Pillar 3 Reports 2024 (PDF p.59) and 2025 (PDF p.55) state under Art. 437a 'MREL disclosures are not applicable for Barclays Bank PLC', pointing to TLAC2 in the Barclays PLC Pillar 3 (creditor ranking, not a ratio); the 2022 and 2023 editions have no MREL text.</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="150" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
+FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
+FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
+FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A5:F5"/>
+    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -9660,6 +9782,257 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
+  <dimension ref="A1:F12"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="59" customWidth="1" min="1" max="1"/>
+    <col width="15" customWidth="1" min="2" max="2"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="15" customWidth="1" min="4" max="4"/>
+    <col width="15" customWidth="1" min="5" max="5"/>
+    <col width="15" customWidth="1" min="6" max="6"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC — Profitability</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="2" t="inlineStr">
+        <is>
+          <t>Return on equity and return on assets in per cent, computed from this workbook's own Balance Sheet and Profit &amp; Loss sheets.</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t>Metric</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C3" s="4" t="inlineStr">
+        <is>
+          <t>FY2024</t>
+        </is>
+      </c>
+      <c r="D3" s="4" t="inlineStr">
+        <is>
+          <t>FY2023</t>
+        </is>
+      </c>
+      <c r="E3" s="4" t="inlineStr">
+        <is>
+          <t>FY2022</t>
+        </is>
+      </c>
+      <c r="F3" s="4" t="inlineStr">
+        <is>
+          <t>FY2021</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - average equity basis</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="inlineStr">
+        <is>
+          <t>7.67%</t>
+        </is>
+      </c>
+      <c r="C4" s="6" t="inlineStr">
+        <is>
+          <t>6.26%</t>
+        </is>
+      </c>
+      <c r="D4" s="6" t="inlineStr">
+        <is>
+          <t>5.96%</t>
+        </is>
+      </c>
+      <c r="E4" s="6" t="inlineStr">
+        <is>
+          <t>7.60%</t>
+        </is>
+      </c>
+      <c r="F4" s="6" t="n"/>
+    </row>
+    <row r="5">
+      <c r="A5" s="6" t="inlineStr">
+        <is>
+          <t>Return on equity - year-end equity basis</t>
+        </is>
+      </c>
+      <c r="B5" s="6" t="inlineStr">
+        <is>
+          <t>7.48%</t>
+        </is>
+      </c>
+      <c r="C5" s="6" t="inlineStr">
+        <is>
+          <t>6.33%</t>
+        </is>
+      </c>
+      <c r="D5" s="6" t="inlineStr">
+        <is>
+          <t>5.89%</t>
+        </is>
+      </c>
+      <c r="E5" s="6" t="inlineStr">
+        <is>
+          <t>7.43%</t>
+        </is>
+      </c>
+      <c r="F5" s="6" t="inlineStr">
+        <is>
+          <t>8.15%</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - average assets basis</t>
+        </is>
+      </c>
+      <c r="B6" s="6" t="inlineStr">
+        <is>
+          <t>0.38%</t>
+        </is>
+      </c>
+      <c r="C6" s="6" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="D6" s="6" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="E6" s="6" t="inlineStr">
+        <is>
+          <t>0.39%</t>
+        </is>
+      </c>
+      <c r="F6" s="6" t="n"/>
+    </row>
+    <row r="7">
+      <c r="A7" s="6" t="inlineStr">
+        <is>
+          <t>Return on assets - year-end assets basis</t>
+        </is>
+      </c>
+      <c r="B7" s="6" t="inlineStr">
+        <is>
+          <t>0.37%</t>
+        </is>
+      </c>
+      <c r="C7" s="6" t="inlineStr">
+        <is>
+          <t>0.31%</t>
+        </is>
+      </c>
+      <c r="D7" s="6" t="inlineStr">
+        <is>
+          <t>0.30%</t>
+        </is>
+      </c>
+      <c r="E7" s="6" t="inlineStr">
+        <is>
+          <t>0.36%</t>
+        </is>
+      </c>
+      <c r="F7" s="6" t="inlineStr">
+        <is>
+          <t>0.43%</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="6" t="inlineStr">
+        <is>
+          <t>Barclays Bank PLC Group Return on Asset (as published)</t>
+        </is>
+      </c>
+      <c r="B8" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="C8" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D8" s="6" t="n"/>
+      <c r="E8" s="6" t="n"/>
+      <c r="F8" s="6" t="n"/>
+    </row>
+    <row r="9">
+      <c r="A9" s="6" t="inlineStr">
+        <is>
+          <t>Return on Assets (solo-consolidated basis) (as published)</t>
+        </is>
+      </c>
+      <c r="B9" s="6" t="inlineStr">
+        <is>
+          <t>0.4%</t>
+        </is>
+      </c>
+      <c r="C9" s="6" t="inlineStr">
+        <is>
+          <t>Not published</t>
+        </is>
+      </c>
+      <c r="D9" s="6" t="n"/>
+      <c r="E9" s="6" t="n"/>
+      <c r="F9" s="6" t="n"/>
+    </row>
+    <row r="10" ht="234" customHeight="1">
+      <c r="A10" s="7" t="inlineStr">
+        <is>
+          <t>Note: TWO KINDS OF FIGURE, NEVER MERGED. The rows above are not one series. The 'Return on equity/assets' rows are THIS PROJECT'S OWN ARITHMETIC on the figures printed on this workbook's statement sheets. The rows marked '(as published)' are the bank's own published ratios, quoted verbatim, each struck on the bank's own definition - which differs from bank to bank and usually from ours, most often in whether the numerator is before or after tax and whether the denominator is average, opening or year-end equity, tangible equity or required equity. They are not averaged, reconciled, or substituted for one another, and where they disagree both stand: the disagreement is the finding.
+THE BANK'S OWN DEFINITIONS, VERBATIM. Barclays Bank PLC Group Return on Asset: the document states no definition, and none is supplied here. Return on Assets (solo-consolidated basis): the document states no definition, and none is supplied here.
+WHY TWO BASES ARE PRINTED FOR EACH RATIO, AND NEITHER IS PREFERRED. The average basis divides by the mean of the opening and closing balance and is the fairer measure of a year in which the balance sheet moved a long way; the year-end basis divides by the closing balance alone and is what most outside sources quote. Both are shown so the reader can see which question a figure answers. They are not averaged and neither is 'the' return.
+FY2021 HAS NO AVERAGE-BASIS RATIO, AND THAT IS CORRECT. An average denominator needs an opening balance, and FY2021 is the oldest column this workbook carries, so there is no prior year to open from. The blank is structural, not a missing figure. The year-end basis is shown for FY2021 because it needs only the closing balance.
+FIGURES THE BANK PUBLISHED ONLY AS A LATER EDITION'S COMPARATIVE, AND WHY THEY ARE NOT IN THE CELLS ABOVE. FY2024 Return on Assets (solo-consolidated basis) 0.4%; FY2024 Barclays Bank PLC Group Return on Asset 0.3%. Each year's cell carries what that year's OWN annual report printed. A comparative restated in a later edition is a different claim - it may rest on a revised definition, a restated perimeter or a corrected prior figure - so it is recorded here rather than substituted into the year it refers to.</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="170" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>Computed by this workbook's own build script from the Profit &amp; Loss and Balance Sheet sheets of this same workbook - the Profit &amp; Loss row “profit after tax” and the Balance Sheet rows “total equity” and “total assets”, resolved BY LABEL at build time through the shared resolver scripts/profitability_rows.py, so this sheet cannot drift from the statements it summarises. Those rows are themselves transcribed from Barclays Bank PLC's Annual Report and Accounts for each year; see the source cells on the Balance Sheet and Profit &amp; Loss sheets for the exact document, page and table behind every input to every percentage above.
+The '(as published)' rows are quoted verbatim from Barclays Bank PLC's own disclosures and are recorded, with the exact document, page and verification state for each, in research/profitability/published_returns.jsonl under ‘BARCLAYS BANK PLC’.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A10:F10"/>
+    <mergeCell ref="A12:F12"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
   <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
@@ -10805,117 +11178,6 @@
   <mergeCells count="2">
     <mergeCell ref="A59:E59"/>
     <mergeCell ref="A57:E57"/>
-  </mergeCells>
-  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:F7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="44" customWidth="1" min="1" max="1"/>
-    <col width="15" customWidth="1" min="2" max="2"/>
-    <col width="15" customWidth="1" min="3" max="3"/>
-    <col width="15" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="15" customWidth="1" min="6" max="6"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t>Barclays Bank PLC — CET1 Capital</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" s="2" t="inlineStr">
-        <is>
-          <t>Solo-consolidated basis, £m</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>Metric</t>
-        </is>
-      </c>
-      <c r="B3" s="4" t="inlineStr">
-        <is>
-          <t>FY2025</t>
-        </is>
-      </c>
-      <c r="C3" s="4" t="inlineStr">
-        <is>
-          <t>FY2024</t>
-        </is>
-      </c>
-      <c r="D3" s="4" t="inlineStr">
-        <is>
-          <t>FY2023</t>
-        </is>
-      </c>
-      <c r="E3" s="4" t="inlineStr">
-        <is>
-          <t>FY2022</t>
-        </is>
-      </c>
-      <c r="F3" s="4" t="inlineStr">
-        <is>
-          <t>FY2021</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>Common Equity Tier 1 (CET1) capital</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="n">
-        <v>28177</v>
-      </c>
-      <c r="C4" s="6" t="n">
-        <v>26995</v>
-      </c>
-      <c r="D4" s="6" t="n">
-        <v>25470</v>
-      </c>
-      <c r="E4" s="6" t="n">
-        <v>25907</v>
-      </c>
-      <c r="F4" s="6" t="n">
-        <v>23928</v>
-      </c>
-    </row>
-    <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="7" t="inlineStr">
-        <is>
-          <t>Note: FY2021 figure is restated (Over-issuance of Securities matter); see Note 1a in the FY2022 Annual Report.</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="117" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>Sources — Barclays Bank PLC solo-consolidated capital/liquidity disclosures, from the 'Treasury and Capital risk' section of the Risk review, as filed with Companies House:
-FY2025 &amp; FY2024: Barclays Bank PLC Annual Report 2025, p.220-222 (Liquidity risk: Liquidity Pool/LCR/NSFR) and p.231 (Capital risk: Capital ratios/resources/RWAs/Leverage ratio) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzUyMzkyMDY5MmFkaXF6a2N4/document?format=pdf&amp;download=0
-FY2023: Barclays Bank PLC Annual Report 2024, p.213-222 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzQ2OTM2NDcwM2FkaXF6a2N4/document?format=pdf&amp;download=0
-FY2022 &amp; FY2021: Barclays Bank PLC Annual Report 2022, p.115-126 (Liquidity risk / Capital risk) — https://find-and-update.company-information.service.gov.uk/company/01026167/filing-history/MzM4Mjg0NjA2M2FkaXF6a2N4/document?format=pdf&amp;download=0</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A5:F5"/>
-    <mergeCell ref="A7:F7"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -10941,14 +11203,14 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Barclays Bank PLC — CET1 Ratio</t>
+          <t>Barclays Bank PLC — CET1 Capital</t>
         </is>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Solo-consolidated basis, % of RWA</t>
+          <t>Solo-consolidated basis, £m</t>
         </is>
       </c>
     </row>
@@ -10987,33 +11249,23 @@
     <row r="4">
       <c r="A4" s="6" t="inlineStr">
         <is>
-          <t>Common Equity Tier 1 (CET1) ratio</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>12.1%</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>12.7%</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>12.9%</t>
-        </is>
+          <t>Common Equity Tier 1 (CET1) capital</t>
+        </is>
+      </c>
+      <c r="B4" s="6" t="n">
+        <v>28177</v>
+      </c>
+      <c r="C4" s="6" t="n">
+        <v>26995</v>
+      </c>
+      <c r="D4" s="6" t="n">
+        <v>25470</v>
+      </c>
+      <c r="E4" s="6" t="n">
+        <v>25907</v>
+      </c>
+      <c r="F4" s="6" t="n">
+        <v>23928</v>
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
